--- a/main/data/prices.xlsx
+++ b/main/data/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94E64B3-EF79-473C-B08B-25A6A6F3DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B12323-216B-4348-8C17-FF257DF36FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="211">
   <si>
     <t>Категория</t>
   </si>
@@ -587,9 +587,6 @@
     <t>Правила по охране труда при работе в ограниченных и замкнутых пространствах (1, 2, 3 группа)</t>
   </si>
   <si>
-    <t>ч</t>
-  </si>
-  <si>
     <t>Промышленная безопасность</t>
   </si>
   <si>
@@ -848,9 +845,6 @@
     <t>Подготовка по области аттестации Г.2.2 руководителей и специалистов организаций, эксплуатирующих электрические сети</t>
   </si>
   <si>
-    <t>Подготовка и проверка знания норм и правил в области энергетического надзора</t>
-  </si>
-  <si>
     <t>Программа повышения квалификации электротехнического персонала</t>
   </si>
   <si>
@@ -1029,13 +1023,16 @@
   </si>
   <si>
     <t>Программа ПК для лиц, ответственных за обеспечение пожарной безопасности на объектах защиты, в которых могут одновременно находиться 50 и более человек, объектах защиты, отнесенных к категориям повышенной взрывопожароопасности, взрывопожароопасности, пожароопасности</t>
+  </si>
+  <si>
+    <t>Программа ПК электротехнического персонала (обслуживание аккумуляторной батареи)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1044,16 +1041,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="8"/>
-      <color rgb="FF0A0A0A"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1116,6 +1113,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -1204,25 +1208,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1240,9 +1228,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1257,34 +1242,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1573,7 +1565,7 @@
     <col min="2" max="2" width="79.6640625" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1589,7 +1581,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1597,16 +1589,16 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="4">
         <v>240</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="4">
         <v>22600</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1614,16 +1606,16 @@
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="5">
         <v>240</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="5">
         <v>22600</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1631,16 +1623,16 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="5">
         <v>240</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="5">
         <v>22600</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1648,16 +1640,16 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="5">
         <v>240</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="5">
         <v>22600</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1665,16 +1657,16 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="5">
         <v>240</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="5">
         <v>22600</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1682,16 +1674,16 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="5">
         <v>240</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="5">
         <v>22600</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1699,16 +1691,16 @@
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="5">
         <v>240</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="5">
         <v>24800</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1716,16 +1708,16 @@
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="5">
         <v>240</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="5">
         <v>24800</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1733,16 +1725,16 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="5">
         <v>240</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="5">
         <v>24800</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1750,16 +1742,16 @@
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="5">
         <v>240</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="5">
         <v>32400</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1767,16 +1759,16 @@
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="5">
         <v>240</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="5">
         <v>32400</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1784,16 +1776,16 @@
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="5">
         <v>240</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="5">
         <v>32400</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1801,16 +1793,16 @@
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="5">
         <v>240</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="5">
         <v>24800</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1818,16 +1810,16 @@
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="11">
+      <c r="B15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5">
         <v>240</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="5">
         <v>24800</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1835,16 +1827,16 @@
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="5">
         <v>240</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="5">
         <v>24800</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1852,16 +1844,16 @@
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="5">
         <v>240</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="5">
         <v>24800</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1869,16 +1861,16 @@
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="5">
         <v>240</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="5">
         <v>24800</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1886,16 +1878,16 @@
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="5">
         <v>240</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="5">
         <v>24800</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1903,16 +1895,16 @@
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="5">
         <v>240</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="5">
         <v>22600</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1920,16 +1912,16 @@
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="5">
         <v>240</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="5">
         <v>22600</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1937,16 +1929,16 @@
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="5">
         <v>240</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="5">
         <v>22600</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1954,16 +1946,16 @@
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="6">
         <v>240</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="5">
         <v>22600</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1971,16 +1963,16 @@
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="5">
         <v>240</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="5">
         <v>22600</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1988,16 +1980,16 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="5">
         <v>120</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="5">
         <v>8500</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2005,16 +1997,16 @@
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="5">
         <v>240</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="5">
         <v>23000</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2022,16 +2014,16 @@
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="5">
         <v>240</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="5">
         <v>23000</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2039,16 +2031,16 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="5">
         <v>240</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="5">
         <v>23000</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2056,16 +2048,16 @@
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="5">
         <v>240</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="5">
         <v>23000</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2073,16 +2065,16 @@
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="5">
         <v>240</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="5">
         <v>23000</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2090,16 +2082,16 @@
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="5">
         <v>240</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="5">
         <v>23000</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2107,16 +2099,16 @@
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="5">
         <v>240</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="5">
         <v>28000</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2124,16 +2116,16 @@
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="5">
         <v>240</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="5">
         <v>23000</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2141,16 +2133,16 @@
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="5">
         <v>240</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="5">
         <v>23000</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2158,16 +2150,16 @@
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="5">
         <v>264</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="5">
         <v>33000</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2175,16 +2167,16 @@
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="5">
         <v>240</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="5">
         <v>23000</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2192,16 +2184,16 @@
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="5">
         <v>240</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="5">
         <v>22600</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2209,16 +2201,16 @@
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="5">
         <v>240</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="5">
         <v>22600</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2226,16 +2218,16 @@
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="5">
         <v>240</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="5">
         <v>22600</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2243,16 +2235,16 @@
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="5">
         <v>240</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="5">
         <v>22600</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2260,16 +2252,16 @@
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="5">
         <v>240</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="5">
         <v>22600</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="24" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2277,2674 +2269,2674 @@
       <c r="A42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="8">
         <v>40</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="9">
         <v>7500</v>
       </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" s="10"/>
+      <c r="E42" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="5">
         <v>40</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="10">
         <v>5700</v>
       </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="11"/>
+      <c r="E43" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="5">
         <v>40</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="10">
         <v>5700</v>
       </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="11"/>
+      <c r="E44" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="5"/>
     </row>
     <row r="45" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="5">
         <v>72</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="10">
         <v>58000</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="11"/>
+      <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="5">
         <v>24</v>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="11">
         <v>10500</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="11"/>
+      <c r="F46" s="5"/>
     </row>
     <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="12">
+      <c r="B47" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" s="6">
         <v>24</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="10">
         <v>7500</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F47" s="11"/>
+      <c r="F47" s="5"/>
     </row>
     <row r="48" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="5">
         <v>24</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="10">
         <v>7500</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="11"/>
+      <c r="F48" s="5"/>
     </row>
     <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="6">
         <v>24</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="10">
         <v>7500</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F49" s="11"/>
+      <c r="F49" s="5"/>
     </row>
     <row r="50" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="5">
         <v>24</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="10">
         <v>7500</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F50" s="11"/>
+      <c r="F50" s="5"/>
     </row>
     <row r="51" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="5">
         <v>40</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="10">
         <v>7200</v>
       </c>
-      <c r="E51" t="s">
-        <v>89</v>
-      </c>
-      <c r="F51" s="12"/>
+      <c r="E51" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="5">
         <v>40</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="10">
         <v>7200</v>
       </c>
-      <c r="E52" t="s">
-        <v>89</v>
-      </c>
-      <c r="F52" s="12"/>
+      <c r="E52" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F52" s="6"/>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="5">
         <v>72</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="10">
         <v>10500</v>
       </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" s="11"/>
+      <c r="E53" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="5"/>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="5">
         <v>72</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="10">
         <v>10500</v>
       </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="11"/>
+      <c r="E54" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="5"/>
     </row>
     <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="5">
         <v>72</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="10">
         <v>10500</v>
       </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" s="11"/>
+      <c r="E55" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="5"/>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="5">
         <v>72</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="10">
         <v>10500</v>
       </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" s="11"/>
+      <c r="E56" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="5"/>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="5">
         <v>72</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="10">
         <v>10500</v>
       </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" s="11"/>
+      <c r="E57" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="5"/>
     </row>
     <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="5">
         <v>72</v>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="10">
         <v>10500</v>
       </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="11"/>
+      <c r="E58" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="5"/>
     </row>
     <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="5">
         <v>72</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="10">
         <v>10500</v>
       </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="11"/>
+      <c r="E59" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="5"/>
     </row>
     <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="5">
         <v>72</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="10">
         <v>10500</v>
       </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="11"/>
+      <c r="E60" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="5"/>
     </row>
     <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="5">
         <v>80</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D61" s="10">
         <v>11500</v>
       </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="11"/>
+      <c r="E61" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" s="5"/>
     </row>
     <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="5">
         <v>72</v>
       </c>
-      <c r="D62" s="17">
+      <c r="D62" s="10">
         <v>10500</v>
       </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="11"/>
+      <c r="E62" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="5"/>
     </row>
     <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="5">
         <v>72</v>
       </c>
-      <c r="D63" s="17">
+      <c r="D63" s="10">
         <v>11000</v>
       </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" s="11"/>
+      <c r="E63" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="5"/>
     </row>
     <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="5">
         <v>72</v>
       </c>
-      <c r="D64" s="17">
+      <c r="D64" s="10">
         <v>11000</v>
       </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" s="11"/>
+      <c r="E64" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="5"/>
     </row>
     <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="5">
         <v>72</v>
       </c>
-      <c r="D65" s="17">
+      <c r="D65" s="10">
         <v>10500</v>
       </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" s="11"/>
+      <c r="E65" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F65" s="5"/>
     </row>
     <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="6">
         <v>72</v>
       </c>
-      <c r="D66" s="17">
+      <c r="D66" s="10">
         <v>23000</v>
       </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" s="11"/>
+      <c r="E66" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" s="5"/>
     </row>
     <row r="67" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="6">
         <v>72</v>
       </c>
-      <c r="D67" s="17">
+      <c r="D67" s="10">
         <v>23000</v>
       </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" s="11"/>
+      <c r="E67" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="6">
         <v>72</v>
       </c>
-      <c r="D68" s="17">
+      <c r="D68" s="10">
         <v>23000</v>
       </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" s="11"/>
+      <c r="E68" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="6">
         <v>72</v>
       </c>
-      <c r="D69" s="17">
+      <c r="D69" s="10">
         <v>23000</v>
       </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" s="11"/>
+      <c r="E69" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" s="5"/>
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="6">
         <v>72</v>
       </c>
-      <c r="D70" s="17">
+      <c r="D70" s="10">
         <v>23000</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F70" s="12"/>
+      <c r="F70" s="6"/>
     </row>
     <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="6">
         <v>72</v>
       </c>
-      <c r="D71" s="17">
+      <c r="D71" s="10">
         <v>23000</v>
       </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" s="11"/>
+      <c r="E71" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="6">
         <v>24</v>
       </c>
-      <c r="D72" s="18">
+      <c r="D72" s="11">
         <v>7500</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F72" s="12"/>
+      <c r="F72" s="6"/>
     </row>
     <row r="73" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="6">
         <v>24</v>
       </c>
-      <c r="D73" s="17">
+      <c r="D73" s="10">
         <v>6825</v>
       </c>
-      <c r="E73" t="s">
-        <v>89</v>
-      </c>
-      <c r="F73" s="12"/>
+      <c r="E73" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F73" s="6"/>
     </row>
     <row r="74" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="6">
         <v>24</v>
       </c>
-      <c r="D74" s="17">
+      <c r="D74" s="10">
         <v>6825</v>
       </c>
-      <c r="E74" t="s">
-        <v>89</v>
-      </c>
-      <c r="F74" s="12"/>
+      <c r="E74" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F74" s="6"/>
     </row>
     <row r="75" spans="1:6" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="6">
         <v>24</v>
       </c>
-      <c r="D75" s="17">
+      <c r="D75" s="10">
         <v>6825</v>
       </c>
-      <c r="E75" t="s">
-        <v>89</v>
-      </c>
-      <c r="F75" s="12"/>
+      <c r="E75" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F75" s="6"/>
     </row>
     <row r="76" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="6">
         <v>24</v>
       </c>
-      <c r="D76" s="17">
+      <c r="D76" s="10">
         <v>7500</v>
       </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="11"/>
+      <c r="E76" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F76" s="5"/>
     </row>
     <row r="77" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="6">
         <v>24</v>
       </c>
-      <c r="D77" s="17">
+      <c r="D77" s="10">
         <v>7500</v>
       </c>
-      <c r="E77" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" s="11"/>
+      <c r="E77" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" s="5"/>
     </row>
     <row r="78" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="6">
         <v>24</v>
       </c>
-      <c r="D78" s="17">
+      <c r="D78" s="10">
         <v>6825</v>
       </c>
-      <c r="E78" t="s">
-        <v>89</v>
-      </c>
-      <c r="F78" s="12"/>
+      <c r="E78" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F78" s="6"/>
     </row>
     <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="5">
         <v>24</v>
       </c>
-      <c r="D79" s="17">
+      <c r="D79" s="10">
         <v>7500</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F79" s="11"/>
+      <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="6">
         <v>24</v>
       </c>
-      <c r="D80" s="17">
+      <c r="D80" s="10">
         <v>2750</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F80" s="11"/>
+      <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81" s="6">
         <v>40</v>
       </c>
-      <c r="D81" s="18">
+      <c r="D81" s="11">
         <v>3850</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F81" s="12"/>
+      <c r="F81" s="6"/>
     </row>
     <row r="82" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82" s="6">
         <v>16</v>
       </c>
-      <c r="D82" s="19" t="s">
+      <c r="D82" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F82" s="11"/>
+      <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83" s="6">
         <v>24</v>
       </c>
-      <c r="D83" s="18">
+      <c r="D83" s="11">
         <v>3850</v>
       </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" s="11"/>
+      <c r="E83" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B84" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C84" s="15">
+      <c r="B84" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C84" s="8">
         <v>24</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="2">
         <v>2300</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C85" s="6">
         <v>24</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="3">
         <v>2300</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="6">
         <v>24</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="3">
         <v>2300</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="6">
         <v>256</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="3">
         <v>6900</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="C88" s="4">
+        <v>20</v>
+      </c>
+      <c r="D88" s="9">
+        <v>2200</v>
+      </c>
+      <c r="E88" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C88" s="10">
-        <v>20</v>
-      </c>
-      <c r="D88" s="16">
-        <v>2200</v>
-      </c>
-      <c r="E88" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="20" t="s">
+      <c r="C89" s="4">
+        <v>20</v>
+      </c>
+      <c r="D89" s="2">
+        <v>4400</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="10">
-        <v>20</v>
-      </c>
-      <c r="D89" s="8">
+      <c r="C90" s="4">
+        <v>20</v>
+      </c>
+      <c r="D90" s="2">
         <v>4400</v>
       </c>
-      <c r="E89" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="21" t="s">
+      <c r="E90" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C90" s="10">
-        <v>20</v>
-      </c>
-      <c r="D90" s="8">
+      <c r="C91" s="4">
+        <v>20</v>
+      </c>
+      <c r="D91" s="2">
         <v>4400</v>
       </c>
-      <c r="E90" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="22" t="s">
+      <c r="E91" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C91" s="10">
-        <v>20</v>
-      </c>
-      <c r="D91" s="8">
+      <c r="C92" s="4">
+        <v>20</v>
+      </c>
+      <c r="D92" s="2">
         <v>4400</v>
       </c>
-      <c r="E91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="22" t="s">
+      <c r="E92" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="C92" s="10">
-        <v>20</v>
-      </c>
-      <c r="D92" s="8">
+      <c r="C93" s="4">
+        <v>20</v>
+      </c>
+      <c r="D93" s="2">
         <v>4400</v>
       </c>
-      <c r="E92" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B93" s="22" t="s">
+      <c r="E93" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C93" s="10">
-        <v>20</v>
-      </c>
-      <c r="D93" s="8">
+      <c r="C94" s="4">
+        <v>20</v>
+      </c>
+      <c r="D94" s="2">
         <v>4400</v>
       </c>
-      <c r="E93" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" s="22" t="s">
+      <c r="E94" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C94" s="10">
-        <v>20</v>
-      </c>
-      <c r="D94" s="8">
+      <c r="C95" s="4">
+        <v>20</v>
+      </c>
+      <c r="D95" s="2">
         <v>4400</v>
       </c>
-      <c r="E94" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B95" s="22" t="s">
+      <c r="E95" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C95" s="10">
-        <v>20</v>
-      </c>
-      <c r="D95" s="8">
+      <c r="C96" s="4">
+        <v>20</v>
+      </c>
+      <c r="D96" s="2">
         <v>4400</v>
       </c>
-      <c r="E95" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B96" s="22" t="s">
+      <c r="E96" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C96" s="10">
-        <v>20</v>
-      </c>
-      <c r="D96" s="8">
+      <c r="C97" s="4">
+        <v>20</v>
+      </c>
+      <c r="D97" s="2">
         <v>4400</v>
       </c>
-      <c r="E96" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B97" s="22" t="s">
+      <c r="E97" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B98" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C97" s="10">
-        <v>20</v>
-      </c>
-      <c r="D97" s="8">
+      <c r="C98" s="4">
+        <v>20</v>
+      </c>
+      <c r="D98" s="2">
         <v>4400</v>
       </c>
-      <c r="E97" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B98" s="22" t="s">
+      <c r="E98" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B99" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="C98" s="10">
-        <v>20</v>
-      </c>
-      <c r="D98" s="8">
+      <c r="C99" s="4">
+        <v>20</v>
+      </c>
+      <c r="D99" s="2">
         <v>4400</v>
       </c>
-      <c r="E98" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B99" s="21" t="s">
+      <c r="E99" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B100" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C99" s="10">
-        <v>20</v>
-      </c>
-      <c r="D99" s="8">
+      <c r="C100" s="4">
+        <v>20</v>
+      </c>
+      <c r="D100" s="2">
         <v>4400</v>
       </c>
-      <c r="E99" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B100" s="21" t="s">
+      <c r="E100" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C100" s="10">
-        <v>20</v>
-      </c>
-      <c r="D100" s="8">
+      <c r="C101" s="4">
+        <v>20</v>
+      </c>
+      <c r="D101" s="2">
         <v>4400</v>
       </c>
-      <c r="E100" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B101" s="21" t="s">
+      <c r="E101" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="76.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B102" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="C101" s="10">
-        <v>20</v>
-      </c>
-      <c r="D101" s="8">
+      <c r="C102" s="4">
+        <v>20</v>
+      </c>
+      <c r="D102" s="2">
         <v>4400</v>
       </c>
-      <c r="E101" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="76.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B102" s="21" t="s">
+      <c r="E102" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B103" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C102" s="10">
-        <v>20</v>
-      </c>
-      <c r="D102" s="8">
+      <c r="C103" s="4">
+        <v>20</v>
+      </c>
+      <c r="D103" s="2">
         <v>4400</v>
       </c>
-      <c r="E102" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B103" s="22" t="s">
+      <c r="E103" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B104" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C103" s="10">
-        <v>20</v>
-      </c>
-      <c r="D103" s="8">
+      <c r="C104" s="4">
+        <v>20</v>
+      </c>
+      <c r="D104" s="2">
         <v>4400</v>
       </c>
-      <c r="E103" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B104" s="22" t="s">
+      <c r="E104" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B105" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="C104" s="10">
-        <v>20</v>
-      </c>
-      <c r="D104" s="8">
+      <c r="C105" s="4">
+        <v>20</v>
+      </c>
+      <c r="D105" s="2">
         <v>4400</v>
       </c>
-      <c r="E104" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B105" s="22" t="s">
+      <c r="E105" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B106" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C105" s="10">
-        <v>20</v>
-      </c>
-      <c r="D105" s="8">
+      <c r="C106" s="4">
+        <v>20</v>
+      </c>
+      <c r="D106" s="2">
         <v>4400</v>
       </c>
-      <c r="E105" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B106" s="22" t="s">
+      <c r="E106" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B107" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C106" s="10">
-        <v>20</v>
-      </c>
-      <c r="D106" s="8">
+      <c r="C107" s="4">
+        <v>20</v>
+      </c>
+      <c r="D107" s="2">
         <v>4400</v>
       </c>
-      <c r="E106" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B107" s="22" t="s">
+      <c r="E107" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B108" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C107" s="10">
-        <v>20</v>
-      </c>
-      <c r="D107" s="8">
+      <c r="C108" s="4">
+        <v>20</v>
+      </c>
+      <c r="D108" s="2">
         <v>4400</v>
       </c>
-      <c r="E107" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B108" s="23" t="s">
+      <c r="E108" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B109" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C108" s="10">
-        <v>20</v>
-      </c>
-      <c r="D108" s="8">
+      <c r="C109" s="4">
+        <v>20</v>
+      </c>
+      <c r="D109" s="2">
         <v>4400</v>
       </c>
-      <c r="E108" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B109" s="21" t="s">
+      <c r="E109" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B110" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C109" s="10">
-        <v>20</v>
-      </c>
-      <c r="D109" s="8">
+      <c r="C110" s="4">
+        <v>20</v>
+      </c>
+      <c r="D110" s="2">
         <v>4400</v>
       </c>
-      <c r="E109" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B110" s="21" t="s">
+      <c r="E110" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B111" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C110" s="10">
-        <v>20</v>
-      </c>
-      <c r="D110" s="8">
+      <c r="C111" s="4">
+        <v>20</v>
+      </c>
+      <c r="D111" s="2">
         <v>4400</v>
       </c>
-      <c r="E110" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B111" s="21" t="s">
+      <c r="E111" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B112" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C111" s="10">
-        <v>20</v>
-      </c>
-      <c r="D111" s="8">
+      <c r="C112" s="4">
+        <v>20</v>
+      </c>
+      <c r="D112" s="2">
         <v>4400</v>
       </c>
-      <c r="E111" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B112" s="21" t="s">
+      <c r="E112" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B113" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C112" s="10">
-        <v>20</v>
-      </c>
-      <c r="D112" s="8">
+      <c r="C113" s="4">
+        <v>20</v>
+      </c>
+      <c r="D113" s="2">
         <v>4400</v>
       </c>
-      <c r="E112" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B113" s="21" t="s">
+      <c r="E113" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B114" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C113" s="10">
-        <v>20</v>
-      </c>
-      <c r="D113" s="8">
+      <c r="C114" s="4">
+        <v>20</v>
+      </c>
+      <c r="D114" s="2">
         <v>4400</v>
       </c>
-      <c r="E113" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B114" s="23" t="s">
+      <c r="E114" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B115" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C114" s="10">
-        <v>20</v>
-      </c>
-      <c r="D114" s="8">
+      <c r="C115" s="4">
+        <v>20</v>
+      </c>
+      <c r="D115" s="2">
         <v>4400</v>
       </c>
-      <c r="E114" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B115" s="21" t="s">
+      <c r="E115" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B116" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C115" s="10">
-        <v>20</v>
-      </c>
-      <c r="D115" s="8">
+      <c r="C116" s="4">
+        <v>20</v>
+      </c>
+      <c r="D116" s="2">
         <v>4400</v>
       </c>
-      <c r="E115" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B116" s="21" t="s">
+      <c r="E116" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B117" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C116" s="10">
-        <v>20</v>
-      </c>
-      <c r="D116" s="8">
+      <c r="C117" s="4">
+        <v>20</v>
+      </c>
+      <c r="D117" s="2">
         <v>4400</v>
       </c>
-      <c r="E116" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B117" s="21" t="s">
+      <c r="E117" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B118" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C117" s="10">
-        <v>20</v>
-      </c>
-      <c r="D117" s="8">
+      <c r="C118" s="4">
+        <v>20</v>
+      </c>
+      <c r="D118" s="2">
         <v>4400</v>
       </c>
-      <c r="E117" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B118" s="21" t="s">
+      <c r="E118" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B119" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C118" s="10">
-        <v>20</v>
-      </c>
-      <c r="D118" s="8">
+      <c r="C119" s="4">
+        <v>20</v>
+      </c>
+      <c r="D119" s="2">
         <v>4400</v>
       </c>
-      <c r="E118" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B119" s="21" t="s">
+      <c r="E119" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B120" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C119" s="10">
-        <v>20</v>
-      </c>
-      <c r="D119" s="8">
+      <c r="C120" s="4">
+        <v>20</v>
+      </c>
+      <c r="D120" s="2">
         <v>4400</v>
       </c>
-      <c r="E119" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B120" s="21" t="s">
+      <c r="E120" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B121" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C120" s="10">
-        <v>20</v>
-      </c>
-      <c r="D120" s="8">
+      <c r="C121" s="4">
+        <v>20</v>
+      </c>
+      <c r="D121" s="2">
         <v>4400</v>
       </c>
-      <c r="E120" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B121" s="21" t="s">
+      <c r="E121" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B122" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C121" s="10">
-        <v>20</v>
-      </c>
-      <c r="D121" s="8">
+      <c r="C122" s="4">
+        <v>20</v>
+      </c>
+      <c r="D122" s="2">
         <v>4400</v>
       </c>
-      <c r="E121" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B122" s="21" t="s">
+      <c r="E122" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B123" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C122" s="10">
-        <v>20</v>
-      </c>
-      <c r="D122" s="8">
+      <c r="C123" s="4">
+        <v>20</v>
+      </c>
+      <c r="D123" s="2">
         <v>4400</v>
       </c>
-      <c r="E122" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B123" s="21" t="s">
+      <c r="E123" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B124" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C123" s="10">
-        <v>20</v>
-      </c>
-      <c r="D123" s="8">
+      <c r="C124" s="4">
+        <v>20</v>
+      </c>
+      <c r="D124" s="2">
         <v>4400</v>
       </c>
-      <c r="E123" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B124" s="21" t="s">
+      <c r="E124" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B125" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C124" s="10">
-        <v>20</v>
-      </c>
-      <c r="D124" s="8">
+      <c r="C125" s="4">
+        <v>20</v>
+      </c>
+      <c r="D125" s="2">
         <v>4400</v>
       </c>
-      <c r="E124" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B125" s="21" t="s">
+      <c r="E125" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B126" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C125" s="10">
-        <v>20</v>
-      </c>
-      <c r="D125" s="8">
+      <c r="C126" s="4">
+        <v>20</v>
+      </c>
+      <c r="D126" s="2">
         <v>4400</v>
       </c>
-      <c r="E125" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B126" s="21" t="s">
+      <c r="E126" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B127" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C126" s="10">
-        <v>20</v>
-      </c>
-      <c r="D126" s="8">
+      <c r="C127" s="4">
+        <v>20</v>
+      </c>
+      <c r="D127" s="2">
         <v>4400</v>
       </c>
-      <c r="E126" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B127" s="21" t="s">
+      <c r="E127" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B128" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C127" s="10">
-        <v>20</v>
-      </c>
-      <c r="D127" s="8">
+      <c r="C128" s="4">
+        <v>20</v>
+      </c>
+      <c r="D128" s="2">
         <v>4400</v>
       </c>
-      <c r="E127" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B128" s="20" t="s">
+      <c r="E128" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B129" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="C128" s="10">
-        <v>20</v>
-      </c>
-      <c r="D128" s="8">
+      <c r="C129" s="4">
+        <v>20</v>
+      </c>
+      <c r="D129" s="2">
         <v>4400</v>
       </c>
-      <c r="E128" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B129" s="22" t="s">
+      <c r="E129" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B130" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C129" s="10">
-        <v>20</v>
-      </c>
-      <c r="D129" s="8">
+      <c r="C130" s="4">
+        <v>20</v>
+      </c>
+      <c r="D130" s="2">
         <v>4400</v>
       </c>
-      <c r="E129" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B130" s="22" t="s">
+      <c r="E130" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B131" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C130" s="10">
-        <v>20</v>
-      </c>
-      <c r="D130" s="8">
+      <c r="C131" s="4">
+        <v>20</v>
+      </c>
+      <c r="D131" s="2">
         <v>4400</v>
       </c>
-      <c r="E130" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B131" s="22" t="s">
+      <c r="E131" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B132" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C131" s="10">
-        <v>20</v>
-      </c>
-      <c r="D131" s="8">
+      <c r="C132" s="4">
+        <v>20</v>
+      </c>
+      <c r="D132" s="2">
         <v>4400</v>
       </c>
-      <c r="E131" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B132" s="22" t="s">
+      <c r="E132" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B133" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="C132" s="10">
-        <v>20</v>
-      </c>
-      <c r="D132" s="8">
+      <c r="C133" s="4">
+        <v>20</v>
+      </c>
+      <c r="D133" s="2">
         <v>4400</v>
       </c>
-      <c r="E132" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B133" s="22" t="s">
+      <c r="E133" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B134" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="C133" s="10">
-        <v>20</v>
-      </c>
-      <c r="D133" s="8">
+      <c r="C134" s="4">
+        <v>20</v>
+      </c>
+      <c r="D134" s="2">
         <v>4400</v>
       </c>
-      <c r="E133" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B134" s="22" t="s">
+      <c r="E134" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B135" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C134" s="10">
-        <v>20</v>
-      </c>
-      <c r="D134" s="8">
+      <c r="C135" s="4">
+        <v>20</v>
+      </c>
+      <c r="D135" s="2">
         <v>4400</v>
       </c>
-      <c r="E134" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B135" s="22" t="s">
+      <c r="E135" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B136" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="C135" s="10">
-        <v>20</v>
-      </c>
-      <c r="D135" s="8">
+      <c r="C136" s="4">
+        <v>20</v>
+      </c>
+      <c r="D136" s="2">
         <v>4400</v>
       </c>
-      <c r="E135" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B136" s="29" t="s">
+      <c r="E136" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B137" s="26"/>
+      <c r="C137" s="4">
+        <v>20</v>
+      </c>
+      <c r="D137" s="2">
+        <v>4400</v>
+      </c>
+      <c r="E137" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C136" s="10">
-        <v>20</v>
-      </c>
-      <c r="D136" s="8">
-        <v>4400</v>
-      </c>
-      <c r="E136" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B137" s="30"/>
-      <c r="C137" s="10">
-        <v>20</v>
-      </c>
-      <c r="D137" s="8">
-        <v>4400</v>
-      </c>
-      <c r="E137" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="13" t="s">
+      <c r="B138" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="B138" s="24" t="s">
+      <c r="C138" s="4">
+        <v>40</v>
+      </c>
+      <c r="D138" s="9">
+        <v>7900</v>
+      </c>
+      <c r="E138" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="C138" s="10">
+      <c r="C139" s="4">
         <v>40</v>
       </c>
-      <c r="D138" s="16">
+      <c r="D139" s="9">
         <v>7900</v>
       </c>
-      <c r="E138" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B139" s="25" t="s">
+      <c r="E139" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C139" s="10">
+      <c r="C140" s="4">
         <v>40</v>
       </c>
-      <c r="D139" s="16">
+      <c r="D140" s="9">
         <v>7900</v>
       </c>
-      <c r="E139" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B140" s="6" t="s">
+      <c r="E140" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C140" s="10">
+      <c r="C141" s="8">
+        <v>72</v>
+      </c>
+      <c r="D141" s="9">
+        <v>7900</v>
+      </c>
+      <c r="E141" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B142" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C142" s="6">
+        <v>72</v>
+      </c>
+      <c r="D142" s="10">
+        <v>7900</v>
+      </c>
+      <c r="E142" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C143" s="6">
         <v>40</v>
       </c>
-      <c r="D140" s="16">
+      <c r="D143" s="10">
         <v>7900</v>
       </c>
-      <c r="E140" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B141" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C141" s="15">
+      <c r="E143" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B144" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C144" s="6">
+        <v>40</v>
+      </c>
+      <c r="D144" s="10">
+        <v>7900</v>
+      </c>
+      <c r="E144" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B145" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C145" s="8">
         <v>72</v>
       </c>
-      <c r="D141" s="16">
+      <c r="D145" s="9">
         <v>7900</v>
       </c>
-      <c r="E141" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C142" s="12">
+      <c r="E145" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B146" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C146" s="6">
         <v>72</v>
       </c>
-      <c r="D142" s="17">
+      <c r="D146" s="10">
         <v>7900</v>
       </c>
-      <c r="E142" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C143" s="12">
+      <c r="E146" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C147" s="6">
+        <v>72</v>
+      </c>
+      <c r="D147" s="10">
+        <v>7900</v>
+      </c>
+      <c r="E147" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B148" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C148" s="6">
+        <v>72</v>
+      </c>
+      <c r="D148" s="10">
+        <v>7900</v>
+      </c>
+      <c r="E148" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B149" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C149" s="6">
+        <v>72</v>
+      </c>
+      <c r="D149" s="10">
+        <v>7900</v>
+      </c>
+      <c r="E149" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B150" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C150" s="6">
+        <v>72</v>
+      </c>
+      <c r="D150" s="10">
+        <v>7900</v>
+      </c>
+      <c r="E150" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B151" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C151" s="8">
+        <v>72</v>
+      </c>
+      <c r="D151" s="9">
+        <v>8180</v>
+      </c>
+      <c r="E151" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C152" s="6">
+        <v>72</v>
+      </c>
+      <c r="D152" s="10">
+        <v>8180</v>
+      </c>
+      <c r="E152" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B153" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C153" s="6">
+        <v>72</v>
+      </c>
+      <c r="D153" s="10">
+        <v>8180</v>
+      </c>
+      <c r="E153" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B154" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C154" s="6">
+        <v>72</v>
+      </c>
+      <c r="D154" s="10">
+        <v>8180</v>
+      </c>
+      <c r="E154" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C155" s="6">
+        <v>72</v>
+      </c>
+      <c r="D155" s="10">
+        <v>8180</v>
+      </c>
+      <c r="E155" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C156" s="6">
+        <v>72</v>
+      </c>
+      <c r="D156" s="10">
+        <v>8180</v>
+      </c>
+      <c r="E156" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B157" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C157" s="8">
         <v>40</v>
       </c>
-      <c r="D143" s="17">
+      <c r="D157" s="9">
         <v>7900</v>
       </c>
-      <c r="E143" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C144" s="12">
+      <c r="E157" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B158" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C158" s="6">
         <v>40</v>
       </c>
-      <c r="D144" s="17">
+      <c r="D158" s="10">
         <v>7900</v>
       </c>
-      <c r="E144" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B145" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="C145" s="15">
+      <c r="E158" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B159" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C159" s="6">
+        <v>40</v>
+      </c>
+      <c r="D159" s="10">
+        <v>7900</v>
+      </c>
+      <c r="E159" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C160" s="8">
+        <v>16</v>
+      </c>
+      <c r="D160" s="9">
+        <v>2750</v>
+      </c>
+      <c r="E160" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B161" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C161" s="5">
+        <v>16</v>
+      </c>
+      <c r="D161" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E161" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C162" s="5">
+        <v>16</v>
+      </c>
+      <c r="D162" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E162" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C163" s="5">
+        <v>16</v>
+      </c>
+      <c r="D163" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E163" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B164" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C164" s="5">
+        <v>16</v>
+      </c>
+      <c r="D164" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E164" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B165" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C165" s="5">
+        <v>16</v>
+      </c>
+      <c r="D165" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E165" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C166" s="5">
+        <v>16</v>
+      </c>
+      <c r="D166" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E166" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B167" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C167" s="5">
+        <v>16</v>
+      </c>
+      <c r="D167" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E167" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B168" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="C168" s="5">
+        <v>16</v>
+      </c>
+      <c r="D168" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E168" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C169" s="5">
+        <v>16</v>
+      </c>
+      <c r="D169" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E169" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B170" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C170" s="5">
+        <v>16</v>
+      </c>
+      <c r="D170" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E170" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B171" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C171" s="5">
+        <v>16</v>
+      </c>
+      <c r="D171" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E171" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B172" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C172" s="5">
+        <v>16</v>
+      </c>
+      <c r="D172" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E172" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B173" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C173" s="5">
+        <v>16</v>
+      </c>
+      <c r="D173" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E173" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B174" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C174" s="5">
+        <v>16</v>
+      </c>
+      <c r="D174" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E174" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B175" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C175" s="5">
+        <v>16</v>
+      </c>
+      <c r="D175" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E175" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B176" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C176" s="5">
+        <v>16</v>
+      </c>
+      <c r="D176" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E176" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B177" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C177" s="5">
+        <v>16</v>
+      </c>
+      <c r="D177" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E177" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B178" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C178" s="5">
+        <v>16</v>
+      </c>
+      <c r="D178" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E178" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B179" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C179" s="5">
+        <v>16</v>
+      </c>
+      <c r="D179" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E179" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B180" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C180" s="5">
+        <v>16</v>
+      </c>
+      <c r="D180" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B181" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C181" s="5">
+        <v>16</v>
+      </c>
+      <c r="D181" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E181" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B182" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C182" s="5">
+        <v>16</v>
+      </c>
+      <c r="D182" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E182" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B183" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C183" s="5">
+        <v>16</v>
+      </c>
+      <c r="D183" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E183" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B184" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C184" s="5">
+        <v>16</v>
+      </c>
+      <c r="D184" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E184" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B185" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C185" s="5">
+        <v>16</v>
+      </c>
+      <c r="D185" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E185" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B186" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C186" s="8">
+        <v>16</v>
+      </c>
+      <c r="D186" s="13">
+        <v>2100</v>
+      </c>
+      <c r="E186" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C187" s="6">
+        <v>16</v>
+      </c>
+      <c r="D187" s="11">
+        <v>2100</v>
+      </c>
+      <c r="E187" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B188" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C188" s="8">
         <v>72</v>
       </c>
-      <c r="D145" s="16">
-        <v>7900</v>
-      </c>
-      <c r="E145" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C146" s="12">
+      <c r="D188" s="9">
+        <v>7500</v>
+      </c>
+      <c r="E188" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B189" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C189" s="6">
         <v>72</v>
       </c>
-      <c r="D146" s="17">
-        <v>7900</v>
-      </c>
-      <c r="E146" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C147" s="12">
-        <v>72</v>
-      </c>
-      <c r="D147" s="17">
-        <v>7900</v>
-      </c>
-      <c r="E147" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C148" s="12">
-        <v>72</v>
-      </c>
-      <c r="D148" s="17">
-        <v>7900</v>
-      </c>
-      <c r="E148" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C149" s="12">
-        <v>72</v>
-      </c>
-      <c r="D149" s="17">
-        <v>7900</v>
-      </c>
-      <c r="E149" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C150" s="12">
-        <v>72</v>
-      </c>
-      <c r="D150" s="17">
-        <v>7900</v>
-      </c>
-      <c r="E150" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B151" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="C151" s="15">
-        <v>72</v>
-      </c>
-      <c r="D151" s="16">
-        <v>8180</v>
-      </c>
-      <c r="E151" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C152" s="12">
-        <v>72</v>
-      </c>
-      <c r="D152" s="17">
-        <v>8180</v>
-      </c>
-      <c r="E152" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C153" s="12">
-        <v>72</v>
-      </c>
-      <c r="D153" s="17">
-        <v>8180</v>
-      </c>
-      <c r="E153" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C154" s="12">
-        <v>72</v>
-      </c>
-      <c r="D154" s="17">
-        <v>8180</v>
-      </c>
-      <c r="E154" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C155" s="12">
-        <v>72</v>
-      </c>
-      <c r="D155" s="17">
-        <v>8180</v>
-      </c>
-      <c r="E155" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C156" s="12">
-        <v>72</v>
-      </c>
-      <c r="D156" s="17">
-        <v>8180</v>
-      </c>
-      <c r="E156" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B157" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="C157" s="15">
-        <v>40</v>
-      </c>
-      <c r="D157" s="16">
-        <v>7900</v>
-      </c>
-      <c r="E157" t="s">
+      <c r="D189" s="10">
+        <v>7500</v>
+      </c>
+      <c r="E189" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B190" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C190" s="4">
+        <v>16</v>
+      </c>
+      <c r="D190" s="9">
+        <v>21000</v>
+      </c>
+      <c r="E190" s="23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C158" s="12">
-        <v>40</v>
-      </c>
-      <c r="D158" s="17">
-        <v>7900</v>
-      </c>
-      <c r="E158" t="s">
+    <row r="191" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B191" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C191" s="5">
+        <v>16</v>
+      </c>
+      <c r="D191" s="10">
+        <v>21000</v>
+      </c>
+      <c r="E191" s="23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C159" s="12">
-        <v>40</v>
-      </c>
-      <c r="D159" s="17">
-        <v>7900</v>
-      </c>
-      <c r="E159" t="s">
+    <row r="192" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B192" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C192" s="5">
+        <v>16</v>
+      </c>
+      <c r="D192" s="10">
+        <v>21000</v>
+      </c>
+      <c r="E192" s="23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B160" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="C160" s="15">
+    <row r="193" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C193" s="5">
         <v>16</v>
       </c>
-      <c r="D160" s="16">
-        <v>2750</v>
-      </c>
-      <c r="E160" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C161" s="11">
+      <c r="D193" s="10">
+        <v>21000</v>
+      </c>
+      <c r="E193" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B194" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C194" s="5">
         <v>16</v>
       </c>
-      <c r="D161" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E161" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B162" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="C162" s="11">
+      <c r="D194" s="10">
+        <v>21000</v>
+      </c>
+      <c r="E194" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B195" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C195" s="5">
         <v>16</v>
       </c>
-      <c r="D162" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E162" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B163" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="C163" s="11">
+      <c r="D195" s="10">
+        <v>21000</v>
+      </c>
+      <c r="E195" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B196" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C196" s="5">
         <v>16</v>
       </c>
-      <c r="D163" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E163" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B164" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C164" s="11">
-        <v>16</v>
-      </c>
-      <c r="D164" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E164" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B165" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C165" s="11">
-        <v>16</v>
-      </c>
-      <c r="D165" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E165" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B166" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="C166" s="11">
-        <v>16</v>
-      </c>
-      <c r="D166" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E166" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B167" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="C167" s="11">
-        <v>16</v>
-      </c>
-      <c r="D167" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E167" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B168" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="C168" s="11">
-        <v>16</v>
-      </c>
-      <c r="D168" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E168" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B169" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C169" s="11">
-        <v>16</v>
-      </c>
-      <c r="D169" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E169" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B170" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="C170" s="11">
-        <v>16</v>
-      </c>
-      <c r="D170" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E170" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B171" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C171" s="11">
-        <v>16</v>
-      </c>
-      <c r="D171" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E171" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B172" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="C172" s="11">
-        <v>16</v>
-      </c>
-      <c r="D172" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E172" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B173" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="C173" s="11">
-        <v>16</v>
-      </c>
-      <c r="D173" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E173" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B174" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="C174" s="11">
-        <v>16</v>
-      </c>
-      <c r="D174" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E174" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B175" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C175" s="11">
-        <v>16</v>
-      </c>
-      <c r="D175" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E175" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B176" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C176" s="11">
-        <v>16</v>
-      </c>
-      <c r="D176" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E176" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B177" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="C177" s="11">
-        <v>16</v>
-      </c>
-      <c r="D177" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E177" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B178" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="C178" s="11">
-        <v>16</v>
-      </c>
-      <c r="D178" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E178" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B179" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C179" s="11">
-        <v>16</v>
-      </c>
-      <c r="D179" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E179" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B180" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="C180" s="11">
-        <v>16</v>
-      </c>
-      <c r="D180" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E180" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B181" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="C181" s="11">
-        <v>16</v>
-      </c>
-      <c r="D181" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E181" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B182" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="C182" s="11">
-        <v>16</v>
-      </c>
-      <c r="D182" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E182" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B183" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="C183" s="11">
-        <v>16</v>
-      </c>
-      <c r="D183" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E183" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B184" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C184" s="11">
-        <v>16</v>
-      </c>
-      <c r="D184" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E184" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B185" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="C185" s="11">
-        <v>16</v>
-      </c>
-      <c r="D185" s="18">
-        <v>2750</v>
-      </c>
-      <c r="E185" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B186" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C186" s="15">
-        <v>16</v>
-      </c>
-      <c r="D186" s="27">
-        <v>2100</v>
-      </c>
-      <c r="E186" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C187" s="12">
-        <v>16</v>
-      </c>
-      <c r="D187" s="18">
-        <v>2100</v>
-      </c>
-      <c r="E187" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B188" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="C188" s="15">
-        <v>72</v>
-      </c>
-      <c r="D188" s="16">
-        <v>7500</v>
-      </c>
-      <c r="E188" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C189" s="12">
-        <v>72</v>
-      </c>
-      <c r="D189" s="17">
-        <v>7500</v>
-      </c>
-      <c r="E189" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B190" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="C190" s="10">
-        <v>16</v>
-      </c>
-      <c r="D190" s="16">
+      <c r="D196" s="10">
         <v>21000</v>
       </c>
-      <c r="E190" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C191" s="11">
-        <v>16</v>
-      </c>
-      <c r="D191" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E191" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C192" s="11">
-        <v>16</v>
-      </c>
-      <c r="D192" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E192" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C193" s="11">
-        <v>16</v>
-      </c>
-      <c r="D193" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E193" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C194" s="11">
-        <v>16</v>
-      </c>
-      <c r="D194" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E194" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C195" s="11">
-        <v>16</v>
-      </c>
-      <c r="D195" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E195" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C196" s="11">
-        <v>16</v>
-      </c>
-      <c r="D196" s="17">
-        <v>21000</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="E196" s="23" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4953,5 +4945,6 @@
     <mergeCell ref="B136:B137"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/main/data/prices.xlsx
+++ b/main/data/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B12323-216B-4348-8C17-FF257DF36FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E42A05D-F40F-4E09-89C7-9404D01F0DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="211">
   <si>
     <t>Категория</t>
   </si>
@@ -1208,7 +1208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1273,10 +1273,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1558,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F196"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
@@ -3922,16 +3919,18 @@
         <v>89</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B137" s="26"/>
+        <v>146</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>147</v>
+      </c>
       <c r="C137" s="4">
-        <v>20</v>
-      </c>
-      <c r="D137" s="2">
-        <v>4400</v>
+        <v>40</v>
+      </c>
+      <c r="D137" s="9">
+        <v>7900</v>
       </c>
       <c r="E137" s="23" t="s">
         <v>89</v>
@@ -3941,8 +3940,8 @@
       <c r="A138" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B138" s="15" t="s">
-        <v>147</v>
+      <c r="B138" s="16" t="s">
+        <v>148</v>
       </c>
       <c r="C138" s="4">
         <v>40</v>
@@ -3958,8 +3957,8 @@
       <c r="A139" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B139" s="16" t="s">
-        <v>148</v>
+      <c r="B139" s="17" t="s">
+        <v>149</v>
       </c>
       <c r="C139" s="4">
         <v>40</v>
@@ -3971,15 +3970,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B140" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="C140" s="4">
-        <v>40</v>
+      <c r="B140" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C140" s="8">
+        <v>72</v>
       </c>
       <c r="D140" s="9">
         <v>7900</v>
@@ -3988,17 +3987,17 @@
         <v>89</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B141" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C141" s="8">
+      <c r="B141" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C141" s="6">
         <v>72</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D141" s="10">
         <v>7900</v>
       </c>
       <c r="E141" s="23" t="s">
@@ -4010,10 +4009,10 @@
         <v>146</v>
       </c>
       <c r="B142" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C142" s="6">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D142" s="10">
         <v>7900</v>
@@ -4027,7 +4026,7 @@
         <v>146</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C143" s="6">
         <v>40</v>
@@ -4043,30 +4042,30 @@
       <c r="A144" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B144" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C144" s="6">
-        <v>40</v>
-      </c>
-      <c r="D144" s="10">
+      <c r="B144" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C144" s="8">
+        <v>72</v>
+      </c>
+      <c r="D144" s="9">
         <v>7900</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B145" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="C145" s="8">
+      <c r="B145" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C145" s="6">
         <v>72</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D145" s="10">
         <v>7900</v>
       </c>
       <c r="E145" s="23" t="s">
@@ -4078,7 +4077,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C146" s="6">
         <v>72</v>
@@ -4095,7 +4094,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C147" s="6">
         <v>72</v>
@@ -4112,7 +4111,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C148" s="6">
         <v>72</v>
@@ -4129,7 +4128,7 @@
         <v>146</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C149" s="6">
         <v>72</v>
@@ -4141,18 +4140,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B150" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C150" s="6">
+      <c r="B150" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C150" s="8">
         <v>72</v>
       </c>
-      <c r="D150" s="10">
-        <v>7900</v>
+      <c r="D150" s="9">
+        <v>8180</v>
       </c>
       <c r="E150" s="23" t="s">
         <v>7</v>
@@ -4162,13 +4161,13 @@
       <c r="A151" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B151" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C151" s="8">
+      <c r="B151" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C151" s="6">
         <v>72</v>
       </c>
-      <c r="D151" s="9">
+      <c r="D151" s="10">
         <v>8180</v>
       </c>
       <c r="E151" s="23" t="s">
@@ -4180,7 +4179,7 @@
         <v>146</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C152" s="6">
         <v>72</v>
@@ -4197,7 +4196,7 @@
         <v>146</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C153" s="6">
         <v>72</v>
@@ -4214,7 +4213,7 @@
         <v>146</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C154" s="6">
         <v>72</v>
@@ -4231,7 +4230,7 @@
         <v>146</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C155" s="6">
         <v>72</v>
@@ -4243,34 +4242,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B156" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="C156" s="6">
-        <v>72</v>
-      </c>
-      <c r="D156" s="10">
-        <v>8180</v>
+      <c r="B156" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" s="8">
+        <v>40</v>
+      </c>
+      <c r="D156" s="9">
+        <v>7900</v>
       </c>
       <c r="E156" s="23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B157" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C157" s="8">
+      <c r="B157" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C157" s="6">
         <v>40</v>
       </c>
-      <c r="D157" s="9">
+      <c r="D157" s="10">
         <v>7900</v>
       </c>
       <c r="E157" s="23" t="s">
@@ -4282,7 +4281,7 @@
         <v>146</v>
       </c>
       <c r="B158" s="18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C158" s="6">
         <v>40</v>
@@ -4294,46 +4293,46 @@
         <v>88</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B159" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C159" s="6">
-        <v>40</v>
-      </c>
-      <c r="D159" s="10">
-        <v>7900</v>
+        <v>169</v>
+      </c>
+      <c r="B159" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C159" s="8">
+        <v>16</v>
+      </c>
+      <c r="D159" s="9">
+        <v>2750</v>
       </c>
       <c r="E159" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B160" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="C160" s="8">
+      <c r="B160" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C160" s="5">
         <v>16</v>
       </c>
-      <c r="D160" s="9">
+      <c r="D160" s="11">
         <v>2750</v>
       </c>
       <c r="E160" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B161" s="18" t="s">
-        <v>170</v>
+      <c r="B161" s="22" t="s">
+        <v>171</v>
       </c>
       <c r="C161" s="5">
         <v>16</v>
@@ -4345,12 +4344,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B162" s="22" t="s">
-        <v>171</v>
+      <c r="B162" s="20" t="s">
+        <v>172</v>
       </c>
       <c r="C162" s="5">
         <v>16</v>
@@ -4367,7 +4366,7 @@
         <v>169</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C163" s="5">
         <v>16</v>
@@ -4379,12 +4378,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C164" s="5">
         <v>16</v>
@@ -4401,7 +4400,7 @@
         <v>169</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C165" s="5">
         <v>16</v>
@@ -4418,7 +4417,7 @@
         <v>169</v>
       </c>
       <c r="B166" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C166" s="5">
         <v>16</v>
@@ -4430,12 +4429,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C167" s="5">
         <v>16</v>
@@ -4452,7 +4451,7 @@
         <v>169</v>
       </c>
       <c r="B168" s="20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C168" s="5">
         <v>16</v>
@@ -4464,12 +4463,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C169" s="5">
         <v>16</v>
@@ -4486,7 +4485,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C170" s="5">
         <v>16</v>
@@ -4498,12 +4497,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B171" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C171" s="5">
         <v>16</v>
@@ -4520,7 +4519,7 @@
         <v>169</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C172" s="5">
         <v>16</v>
@@ -4532,12 +4531,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C173" s="5">
         <v>16</v>
@@ -4549,12 +4548,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C174" s="5">
         <v>16</v>
@@ -4566,12 +4565,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C175" s="5">
         <v>16</v>
@@ -4588,7 +4587,7 @@
         <v>169</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C176" s="5">
         <v>16</v>
@@ -4600,12 +4599,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B177" s="20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C177" s="5">
         <v>16</v>
@@ -4622,7 +4621,7 @@
         <v>169</v>
       </c>
       <c r="B178" s="20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C178" s="5">
         <v>16</v>
@@ -4634,12 +4633,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B179" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C179" s="5">
         <v>16</v>
@@ -4656,7 +4655,7 @@
         <v>169</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C180" s="5">
         <v>16</v>
@@ -4668,12 +4667,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B181" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C181" s="5">
         <v>16</v>
@@ -4685,12 +4684,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B182" s="20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C182" s="5">
         <v>16</v>
@@ -4702,12 +4701,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B183" s="20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C183" s="5">
         <v>16</v>
@@ -4724,7 +4723,7 @@
         <v>169</v>
       </c>
       <c r="B184" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C184" s="5">
         <v>16</v>
@@ -4740,30 +4739,30 @@
       <c r="A185" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B185" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C185" s="5">
+      <c r="B185" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C185" s="8">
         <v>16</v>
       </c>
-      <c r="D185" s="11">
-        <v>2750</v>
+      <c r="D185" s="13">
+        <v>2100</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B186" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C186" s="8">
+      <c r="B186" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C186" s="6">
         <v>16</v>
       </c>
-      <c r="D186" s="13">
+      <c r="D186" s="11">
         <v>2100</v>
       </c>
       <c r="E186" s="23" t="s">
@@ -4771,67 +4770,67 @@
       </c>
     </row>
     <row r="187" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B187" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C187" s="6">
-        <v>16</v>
-      </c>
-      <c r="D187" s="11">
-        <v>2100</v>
+      <c r="A187" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B187" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C187" s="8">
+        <v>72</v>
+      </c>
+      <c r="D187" s="9">
+        <v>7500</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B188" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="C188" s="8">
+      <c r="B188" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C188" s="6">
         <v>72</v>
       </c>
-      <c r="D188" s="9">
+      <c r="D188" s="10">
         <v>7500</v>
       </c>
       <c r="E188" s="23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B189" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="C189" s="6">
-        <v>72</v>
-      </c>
-      <c r="D189" s="10">
-        <v>7500</v>
+        <v>200</v>
+      </c>
+      <c r="B189" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C189" s="4">
+        <v>16</v>
+      </c>
+      <c r="D189" s="9">
+        <v>21000</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B190" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C190" s="4">
+      <c r="B190" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C190" s="5">
         <v>16</v>
       </c>
-      <c r="D190" s="9">
+      <c r="D190" s="10">
         <v>21000</v>
       </c>
       <c r="E190" s="23" t="s">
@@ -4843,7 +4842,7 @@
         <v>200</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C191" s="5">
         <v>16</v>
@@ -4855,12 +4854,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B192" s="18" t="s">
-        <v>203</v>
+      <c r="B192" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="C192" s="5">
         <v>16</v>
@@ -4876,8 +4875,8 @@
       <c r="A193" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B193" s="17" t="s">
-        <v>204</v>
+      <c r="B193" s="18" t="s">
+        <v>205</v>
       </c>
       <c r="C193" s="5">
         <v>16</v>
@@ -4894,7 +4893,7 @@
         <v>200</v>
       </c>
       <c r="B194" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C194" s="5">
         <v>16</v>
@@ -4911,7 +4910,7 @@
         <v>200</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C195" s="5">
         <v>16</v>
@@ -4923,27 +4922,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="B196" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C196" s="5">
-        <v>16</v>
-      </c>
-      <c r="D196" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E196" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B136:B137"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/main/data/prices.xlsx
+++ b/main/data/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E42A05D-F40F-4E09-89C7-9404D01F0DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B651AF-9B35-4C3E-8798-73A960F4B126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -905,9 +905,6 @@
     <t>Охрана труда</t>
   </si>
   <si>
-    <t>Обучение Безопасным методам и приемам выполнения работ при воздействии вредных и (или) опасных производственных факторов, источников опасности, идентифицированных в рамках специальной оценки условий труда и оценки профессиональных рисков (Б)</t>
-  </si>
-  <si>
     <t>Безопасные методы и приемы выполнения земляных работ</t>
   </si>
   <si>
@@ -1026,6 +1023,9 @@
   </si>
   <si>
     <t>Программа ПК электротехнического персонала (обслуживание аккумуляторной батареи)</t>
+  </si>
+  <si>
+    <t>Обучение безопасным методам и приемам выполнения работ при воздействии вредных и (или) опасных производственных факторов, источников опасности, идентифицированных в рамках специальной оценки условий труда и оценки профессиональных рисков (Б)</t>
   </si>
 </sst>
 </file>
@@ -2357,7 +2357,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C47" s="6">
         <v>24</v>
@@ -3023,7 +3023,7 @@
         <v>90</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C84" s="8">
         <v>24</v>
@@ -4298,7 +4298,7 @@
         <v>169</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C159" s="8">
         <v>16</v>
@@ -4315,7 +4315,7 @@
         <v>169</v>
       </c>
       <c r="B160" s="18" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="C160" s="5">
         <v>16</v>
@@ -4332,7 +4332,7 @@
         <v>169</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C161" s="5">
         <v>16</v>
@@ -4349,7 +4349,7 @@
         <v>169</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C162" s="5">
         <v>16</v>
@@ -4366,7 +4366,7 @@
         <v>169</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C163" s="5">
         <v>16</v>
@@ -4383,7 +4383,7 @@
         <v>169</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C164" s="5">
         <v>16</v>
@@ -4400,7 +4400,7 @@
         <v>169</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C165" s="5">
         <v>16</v>
@@ -4417,7 +4417,7 @@
         <v>169</v>
       </c>
       <c r="B166" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C166" s="5">
         <v>16</v>
@@ -4434,7 +4434,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C167" s="5">
         <v>16</v>
@@ -4451,7 +4451,7 @@
         <v>169</v>
       </c>
       <c r="B168" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C168" s="5">
         <v>16</v>
@@ -4468,7 +4468,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C169" s="5">
         <v>16</v>
@@ -4485,7 +4485,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C170" s="5">
         <v>16</v>
@@ -4502,7 +4502,7 @@
         <v>169</v>
       </c>
       <c r="B171" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C171" s="5">
         <v>16</v>
@@ -4519,7 +4519,7 @@
         <v>169</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C172" s="5">
         <v>16</v>
@@ -4536,7 +4536,7 @@
         <v>169</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C173" s="5">
         <v>16</v>
@@ -4553,7 +4553,7 @@
         <v>169</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C174" s="5">
         <v>16</v>
@@ -4570,7 +4570,7 @@
         <v>169</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C175" s="5">
         <v>16</v>
@@ -4587,7 +4587,7 @@
         <v>169</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C176" s="5">
         <v>16</v>
@@ -4604,7 +4604,7 @@
         <v>169</v>
       </c>
       <c r="B177" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C177" s="5">
         <v>16</v>
@@ -4621,7 +4621,7 @@
         <v>169</v>
       </c>
       <c r="B178" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C178" s="5">
         <v>16</v>
@@ -4638,7 +4638,7 @@
         <v>169</v>
       </c>
       <c r="B179" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C179" s="5">
         <v>16</v>
@@ -4655,7 +4655,7 @@
         <v>169</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C180" s="5">
         <v>16</v>
@@ -4672,7 +4672,7 @@
         <v>169</v>
       </c>
       <c r="B181" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C181" s="5">
         <v>16</v>
@@ -4689,7 +4689,7 @@
         <v>169</v>
       </c>
       <c r="B182" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C182" s="5">
         <v>16</v>
@@ -4706,7 +4706,7 @@
         <v>169</v>
       </c>
       <c r="B183" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C183" s="5">
         <v>16</v>
@@ -4723,7 +4723,7 @@
         <v>169</v>
       </c>
       <c r="B184" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C184" s="5">
         <v>16</v>
@@ -4740,7 +4740,7 @@
         <v>169</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C185" s="8">
         <v>16</v>
@@ -4757,7 +4757,7 @@
         <v>169</v>
       </c>
       <c r="B186" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C186" s="6">
         <v>16</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="187" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B187" s="15" t="s">
         <v>197</v>
-      </c>
-      <c r="B187" s="15" t="s">
-        <v>198</v>
       </c>
       <c r="C187" s="8">
         <v>72</v>
@@ -4788,10 +4788,10 @@
     </row>
     <row r="188" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C188" s="6">
         <v>72</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="189" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B189" s="16" t="s">
         <v>200</v>
-      </c>
-      <c r="B189" s="16" t="s">
-        <v>201</v>
       </c>
       <c r="C189" s="4">
         <v>16</v>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="190" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B190" s="18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C190" s="5">
         <v>16</v>
@@ -4839,10 +4839,10 @@
     </row>
     <row r="191" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C191" s="5">
         <v>16</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="192" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B192" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C192" s="5">
         <v>16</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="193" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C193" s="5">
         <v>16</v>
@@ -4890,10 +4890,10 @@
     </row>
     <row r="194" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B194" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C194" s="5">
         <v>16</v>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="195" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C195" s="5">
         <v>16</v>

--- a/main/data/prices.xlsx
+++ b/main/data/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B651AF-9B35-4C3E-8798-73A960F4B126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EC0B53-300E-4079-A5EE-AAD9498B8088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>Машинист  котлов</t>
   </si>
   <si>
-    <t>Машинист автовышки и автогидроподъемника</t>
-  </si>
-  <si>
     <t>Машинист крана автомобильного</t>
   </si>
   <si>
@@ -117,39 +114,6 @@
     <t>Стропальщик</t>
   </si>
   <si>
-    <t>Электромонтер оперативно-выездной бригады</t>
-  </si>
-  <si>
-    <t>Электромонтер по испытаниям и измерениям</t>
-  </si>
-  <si>
-    <t>Электромонтер по обслуживанию подстанций</t>
-  </si>
-  <si>
-    <t>Электромонтер по ремонту и обслуживанию электрооборудования</t>
-  </si>
-  <si>
-    <t>Электромонтер по ремонту аппаратуры релейной защиты и автоматики</t>
-  </si>
-  <si>
-    <t>Электромонтер по ремонту воздушных линий электропередачи</t>
-  </si>
-  <si>
-    <t>Электромонтер по ремонту и монтажу кабельных линий</t>
-  </si>
-  <si>
-    <t>Электромонтер по эксплуатации  распределительных сетей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Электромонтер по эксплуатации электросчетчиков  </t>
-  </si>
-  <si>
-    <t>Электромонтер по эксплуатации электросчетчиков  (и работа под напряжением)</t>
-  </si>
-  <si>
-    <t>Электромонтер по обслуживанию электроустановок</t>
-  </si>
-  <si>
     <t>Электросварщик ручной сварки</t>
   </si>
   <si>
@@ -169,9 +133,6 @@
   </si>
   <si>
     <t>Повышение квалификации</t>
-  </si>
-  <si>
-    <t>Преподаватель  по обучению приемам оказания первой помощи</t>
   </si>
   <si>
     <r>
@@ -244,160 +205,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Программа ПК: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>«Оперативное обслуживание электроустановок до 1000 В. Работы под напряжением по замене однофазного счетчика электроэнергии до 1000 В»</t>
-    </r>
-  </si>
-  <si>
     <t>Программа ПК: «Предэкзаменационная подготовка руководителей и специалистов опасных производственных объектов по промышленной безопасности»</t>
   </si>
   <si>
     <t>Программа ПК: «Предэкзаменационная подготовка руководителей и специалистов опасных производственных объектов по энергетической безопасности»</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер  оперативно-выездной бригады</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер по испытаниям и измерениям</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер по обслуживанию подстанций</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер по ремонту аппаратуры релейной защиты и автоматики</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер по ремонту воздушных линий электропередачи</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер по ремонту и монтажу кабельных линий</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер по эксплуатации распределительных сетей</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">Электромонтер по эксплуатации электросчетчиков </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Электромонтер по эксплуатации электросчетчиков  (и работа под напряжением)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -441,21 +252,6 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t>Машинист автовышки и автогидроподъемника</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Программа ПК </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
       <t>Электрослесарь по ремонту оборудования распределительных устройств</t>
     </r>
   </si>
@@ -491,15 +287,6 @@
   </si>
   <si>
     <t>Программа ПК для рабочих, занятых эксплуатацией и ремонтом газового оборудования (индивидуальных баллонных установок и газовых горелок)</t>
-  </si>
-  <si>
-    <t>Программа ПК для рабочих, осуществляющих транспортировку, хранение и эксплуатацию баллонов со сжатыми, сжиженными и растворенными под давлением газами</t>
-  </si>
-  <si>
-    <t>Программа ПК для рабочих по управлению подъемными сооружениями грузоподъемностью до 10 тонн включительно, управляемыми с пола</t>
-  </si>
-  <si>
-    <t>Программа ПК для рабочих люльки, находящихся на подъемнике (вышке)</t>
   </si>
   <si>
     <r>
@@ -572,9 +359,6 @@
     <t>Пожарная безопасность</t>
   </si>
   <si>
-    <t>Программа ПК ответственных должностных лиц, занимающих должности главных специалистов технического и производственного профиля, должностных лиц, исполняющих их обязанности, на объектах защиты, в которых могут одновременно находиться 50 и более человек, объектах защиты, отнесенных к категориям повышенной взрывопожароопасности, взрывопожароопасности, пожароопасности</t>
-  </si>
-  <si>
     <t>Программа ПК лиц, на которых возложена трудовая функция по проведению противопожарного инструктажа</t>
   </si>
   <si>
@@ -647,24 +431,6 @@
     <t>Подготовка по области аттестации Б.1.18 руководителей и специалистов организаций, эксплуатирующих опасные производственные объекты производства шин, резинотехнических и латексных изделий</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Подготовка по области аттестации Б.1.19 руководителей и специалистов организаций, эксплуатирующих </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Химически опасные производственные объекты наземных складов жидкого аммиака</t>
-    </r>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Б.7.1 руководителей и специалистов организаций, эксплуатирующих(включая техническое обслуживание, техническое диагностировании, текущий ремонт) сетей газораспределения и газопотребления</t>
-  </si>
-  <si>
     <t>Подготовка по области аттестации Б.7.2 руководителей и специалистов организаций, эксплуатирующих сети газораспределения и газопотребления тепловых электрических станций</t>
   </si>
   <si>
@@ -674,12 +440,6 @@
     <t>Подготовка по области аттестации Б.7.4 руководителей и специалистов организаций, эксплуатирующих объекты, использующих сжиженные углеводородные газы</t>
   </si>
   <si>
-    <t>Подготовка по области аттестации Б.7.5 руководителей и специалистов организаций, осуществляющих проектирование, строительство, реконструкцию, техническое перевооружение и капитальный ремонт сетей газораспределения и газопотребления»</t>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Б.7.6 руководителей и специалистов организаций, эксплуатирующих автогазозаправочные станции газомоторного топлива»</t>
-  </si>
-  <si>
     <t>Подготовка по области аттестации Б.8.1 руководителей и специалистов организаций, эксплуатирующих опасные производственные объекты, на которых используются котлы (паровые, водогрейные, электрические, а также с органическими и неорганическими теплоносителями)</t>
   </si>
   <si>
@@ -710,97 +470,7 @@
     <t>Подготовка по области аттестации Б.8.5 руководителей и специалистов организаций, эксплуатирующих опасные производственные объекты, на которых используются водолазные барокамеры</t>
   </si>
   <si>
-    <t>Подготовка по области аттестации Б.8.6 руководителей и специалистов организаций, осуществляющих Проектирование, строительство, реконструкция, капитальный ремонт и техническое перевооружение опасных производственных объектов, изготовление, монтаж (демонтаж), обслуживание и ремонт (модернизация) с применением сварки и наладка оборудования, работающего под избыточным давлением, используемого на опасных производственных объектах</t>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Б.8.6.1 руководителей и специалистов организаций, осуществляющих Проектирование, строительство, реконструкция, капитальный ремонт и техническое перевооружение опасных производственных объектов, на которых используется оборудование, работающее под избыточным давлением</t>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Б.8.6.2 руководителей и специалистов организаций, осуществляющих Изготовление, монтаж (демонтаж), обслуживание и ремонт (реконструкция) с применением сварки и наладка оборудования, работающего под избыточным давлением, используемого на опасных производственных объектах</t>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Б.8.7 руководителей и специалистов организаций, осуществляющих Наполнение, техническое освидетельствование и ремонт баллонов для хранения и транспортирования сжатых, сжиженных и растворенных под давлением газов, применяемых на опасных производственных объектах</t>
-  </si>
-  <si>
     <t>Подготовка по области аттестации Б.9.1 руководителей и специалистов организаций, осуществляющих эксплуатацию и капитальный ремонт опасных производственных объектов, на которых используются эскалаторы в метрополитенах, эксплуатацию (в том числе обслуживание и ремонт) эскалаторов в метрополитенах</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Подготовка по области аттестации Б.9.2 руководителей и специалистов организаций, осуществляющих </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Проектирование, строительство, реконструкция, техническое перевооружение, консервация и ликвидация опасных производственных объектов, на которых используются эскалаторы в метрополитенах, а также изготовление, монтаж и наладка эскалаторов</t>
-    </r>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Б.9.3 руководителей и специалистов организаций, эксплуатирующих опасные производственные объекты, на которых используются подъемные сооружения</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Подготовка по области аттестации Б.9.4 руководителей и специалистов организаций, осуществляющих </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Проектирование, строительство, реконструкция, техническое перевооружение, капитальный ремонт, консервация, ликвидация опасных производственных объектов, на которых используются подъемные сооружения</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Подготовка по области аттестации Б.9.5 руководителей и специалистов организаций, осуществляющих </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Монтаж, наладка, обслуживание, ремонт, реконструкция или модернизация подъемных сооружений, применяемых на опасных производственных объектах</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Подготовка по области аттестации Б.9.6 руководителей и специалистов организаций, осуществляющих эксплуатацию и капитальный ремонт опасных производственных объектов, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Эксплуатация и капитальный ремонт, на которых используются пассажирские канатные дороги и (или) фуникулеры, эксплуатация (в том числе обслуживание и ремонт) пассажирских канатных дорог и (или) фуникулеров</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Подготовка по области аттестации Б.9.7 руководителей и специалистов организаций, осуществляющих </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Проектирование, строительство, реконструкция, техническое перевооружение, консервация и ликвидация опасных производственных объектов, на которых используются пассажирские канатные дороги и (или) фуникулеры, а также изготовление, монтаж и наладка пассажирских канатных дорог и (или) фуникулеров</t>
-    </r>
   </si>
   <si>
     <r>
@@ -818,6 +488,336 @@
     </r>
   </si>
   <si>
+    <t>Энергетическая безопасность</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Г.1.1 руководителей и специалистов организаций, эксплуатирующих электроустановки</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Г.2.1 руководителей и специалистов организаций, эксплуатирующих тепловые электрические станции</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Г.2.2 руководителей и специалистов организаций, эксплуатирующих электрические сети</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации электротехнического персонала</t>
+  </si>
+  <si>
+    <t>Повышение квалификации руководителей и специалистов организаций, эксплуатирующих тепловые энергоустановки</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (II группа по электробезопасности до и выше 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (III группа по электробезопасности до 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (III группа по электробезопасности до и выше 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (IV группа по электробезопасности до 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (V группа по электробезопасности до и выше 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (III группа по электробезопасности до и выше 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (III группа по электробезопасности до 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (IV группа по электробезопасности до и выше 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (V группа по электробезопасности до и выше 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (V группа по электробезопасности до 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников теплоснабжающих и теплосетевых организаций</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей тепловой энергии, эксплуатирующих технологическое оборудование, использующее тепловую энергию</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей тепловой энергии, эксплуатирующих системы отопления</t>
+  </si>
+  <si>
+    <t>Охрана труда</t>
+  </si>
+  <si>
+    <t>Обучение по оказанию первой помощи пострадавшим</t>
+  </si>
+  <si>
+    <t>Обучение по использованию (применению) СИЗ</t>
+  </si>
+  <si>
+    <t>Экологическая безопасность</t>
+  </si>
+  <si>
+    <t>Основы обеспечения экологической безопасности в организации</t>
+  </si>
+  <si>
+    <t>Сбор, транспортирование, обработка, утилизация, обезвреживание, размещение отходов I - IV классов опасности</t>
+  </si>
+  <si>
+    <t>Психология</t>
+  </si>
+  <si>
+    <t>Психологические аспекты охраны труда и безопасности работ на энергетических предприятиях</t>
+  </si>
+  <si>
+    <t>Психологические аспекты управленческого труда для руководителей среднего звена и кадрового резерва (стресс и его последствия, способы преодоления кризисных ситуаций)</t>
+  </si>
+  <si>
+    <t>Психологические аспекты управленческого труда для руководителей среднего звена и кадрового резерва (конфликтология, формирование навыков эффективного общения)</t>
+  </si>
+  <si>
+    <t>Программа повышения квалификации кадрового резерва</t>
+  </si>
+  <si>
+    <t>Тренинг для наставников</t>
+  </si>
+  <si>
+    <t>Формирование навыков эффективного общения</t>
+  </si>
+  <si>
+    <t>Психология и этика деловых отношений</t>
+  </si>
+  <si>
+    <t>Обучение по общим вопросам охраны труда и функционирования СУОТ (А)</t>
+  </si>
+  <si>
+    <t>Программа ПК электротехнического персонала (обслуживание аккумуляторной батареи)</t>
+  </si>
+  <si>
+    <t>Машинист автовышки и автогидроподъёмника</t>
+  </si>
+  <si>
+    <t>Электромонтёр оперативно-выездной бригады</t>
+  </si>
+  <si>
+    <t>Электромонтёр по испытаниям и измерениям</t>
+  </si>
+  <si>
+    <t>Электромонтёр по обслуживанию подстанций</t>
+  </si>
+  <si>
+    <t>Электромонтёр по ремонту и обслуживанию электрооборудования</t>
+  </si>
+  <si>
+    <t>Электромонтёр по ремонту аппаратуры релейной защиты и автоматики</t>
+  </si>
+  <si>
+    <t>Электромонтёр по ремонту воздушных линий электропередачи</t>
+  </si>
+  <si>
+    <t>Электромонтёр по ремонту и монтажу кабельных линий</t>
+  </si>
+  <si>
+    <t>Электромонтёр по обслуживанию электроустановок</t>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр по испытаниям и измерениям</t>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр по обслуживанию подстанций</t>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр по ремонту аппаратуры релейной защиты и автоматики</t>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр по ремонту воздушных линий электропередачи</t>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр по ремонту и монтажу кабельных линий</t>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр по эксплуатации распределительных сетей</t>
+  </si>
+  <si>
+    <t>Электромонтёр по эксплуатации распределительных сетей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электромонтёр по эксплуатации электросчётчиков  </t>
+  </si>
+  <si>
+    <t>Электромонтёр по эксплуатации электросчётчиков (и работа под напряжением)</t>
+  </si>
+  <si>
+    <t>Преподаватель по обучению приёмам оказания первой помощи</t>
+  </si>
+  <si>
+    <t>Программа ПК для рабочих люльки, находящихся на подъёмнике (вышке)</t>
+  </si>
+  <si>
+    <t>Программа ПК для рабочих по управлению подъёмными сооружениями грузоподъёмностью до 10 тонн включительно, управляемыми с пола</t>
+  </si>
+  <si>
+    <t>Программа ПК для рабочих, осуществляющих транспортировку, хранение и эксплуатацию баллонов со сжатыми, сжиженными и растворёнными под давлением газами</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Программа ПК </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Машинист автовышки и автогидроподъёмника</t>
+    </r>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр оперативно-выездной бригады</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Программа ПК Электромонтёр по эксплуатации электросчётчиков </t>
+  </si>
+  <si>
+    <t>Программа ПК Электромонтёр по эксплуатации электросчётчиков (и работа под напряжением)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Программа ПК: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>«Оперативное обслуживание электроустановок до 1000 В. Работы под напряжением по замене однофазного счётчика электроэнергии до 1000 В»</t>
+    </r>
+  </si>
+  <si>
+    <t>Программа ПК для лиц, ответственных за обеспечение пожарной безопасности на объектах защиты, в которых могут одновременно находиться 50 и более человек, объектах защиты, отнесённых к категориям повышенной взрывопожароопасности, взрывопожароопасности, пожароопасности</t>
+  </si>
+  <si>
+    <t>Программа ПК ответственных должностных лиц, занимающих должности главных специалистов технического и производственного профиля, должностных лиц, исполняющих их обязанности, на объектах защиты, в которых могут одновременно находиться 50 и более человек, объектах защиты, отнесённых к категориям повышенной взрывопожароопасности, взрывопожароопасности, пожароопасности</t>
+  </si>
+  <si>
+    <r>
+      <t>Подготовка по области аттестации Б.1.19 руководителей и специалистов организаций, эксплуатирующих х</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>имически опасные производственные объекты наземных складов жидкого аммиака</t>
+    </r>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.7.1 руководителей и специалистов организаций, эксплуатирующих (включая техническое обслуживание, техническое диагностировании, текущий ремонт) сетей газораспределения и газопотребления</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.7.5 руководителей и специалистов организаций, осуществляющих проектирование, строительство, реконструкцию, техническое перевооружение и капитальный ремонт сетей газораспределения и газопотребления</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.7.6 руководителей и специалистов организаций, эксплуатирующих автогазозаправочные станции газомоторного топлива</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.8.6 руководителей и специалистов организаций, осуществляющих проектирование, строительство, реконструкция, капитальный ремонт и техническое перевооружение опасных производственных объектов, изготовление, монтаж (демонтаж), обслуживание и ремонт (модернизация) с применением сварки и наладка оборудования, работающего под избыточным давлением, используемого на опасных производственных объектах</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.8.6.1 руководителей и специалистов организаций, осуществляющих проектирование, строительство, реконструкция, капитальный ремонт и техническое перевооружение опасных производственных объектов, на которых используется оборудование, работающее под избыточным давлением</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.8.6.2 руководителей и специалистов организаций, осуществляющих изготовление, монтаж (демонтаж), обслуживание и ремонт (реконструкция) с применением сварки и наладка оборудования, работающего под избыточным давлением, используемого на опасных производственных объектах</t>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.8.7 руководителей и специалистов организаций, осуществляющих наполнение, техническое освидетельствование и ремонт баллонов для хранения и транспортирования сжатых, сжиженных и растворённых под давлением газов, применяемых на опасных производственных объектах</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Подготовка по области аттестации Б.9.2 руководителей и специалистов организаций, осуществляющих </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>проектирование, строительство, реконструкция, техническое перевооружение, консервация и ликвидация опасных производственных объектов, на которых используются эскалаторы в метрополитенах, а также изготовление, монтаж и наладка эскалаторов</t>
+    </r>
+  </si>
+  <si>
+    <t>Подготовка по области аттестации Б.9.3 руководителей и специалистов организаций, эксплуатирующих опасные производственные объекты, на которых используются подъёмные сооружения</t>
+  </si>
+  <si>
+    <r>
+      <t>Подготовка по области аттестации Б.9.4 руководителей и специалистов организаций, осуществляющих п</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>роектирование, строительство, реконструкция, техническое перевооружение, капитальный ремонт, консервация, ликвидация опасных производственных объектов, на которых используются подъёмные сооружения</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Подготовка по области аттестации Б.9.5 руководителей и специалистов организаций, осуществляющих </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>монтаж, наладка, обслуживание, ремонт, реконструкция или модернизация подъёмных сооружений, применяемых на опасных производственных объектах</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Подготовка по области аттестации Б.9.6 руководителей и специалистов организаций, осуществляющих эксплуатацию и капитальный ремонт опасных производственных объектов, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>эксплуатация и капитальный ремонт, на которых используются пассажирские канатные дороги и (или) фуникулёры, эксплуатация (в том числе обслуживание и ремонт) пассажирских канатных дорог и (или) фуникулёров</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Подготовка по области аттестации Б.9.7 руководителей и специалистов организаций, осуществляющих п</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>роектирование, строительство, реконструкция, техническое перевооружение, консервация и ликвидация опасных производственных объектов, на которых используются пассажирские канатные дороги и (или) фуникулёры, а также изготовление, монтаж и наладка пассажирских канатных дорог и (или) фуникулёров</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Подготовка по области аттестации Б.9.9 руководителей и специалистов организаций, осуществляющих </t>
     </r>
@@ -829,203 +829,95 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t>Проектирование, строительство, реконструкция, техническое перевооружение, консервация и ликвидация опасных производственных объектов, на которых используются грузовые подвесные канатные дороги, а также изготовление, монтаж и наладка грузовых подвесных канатных дорог</t>
+      <t>проектирование, строительство, реконструкция, техническое перевооружение, консервация и ликвидация опасных производственных объектов, на которых используются грузовые подвесные канатные дороги, а также изготовление, монтаж и наладка грузовых подвесных канатных дорог</t>
     </r>
   </si>
   <si>
-    <t>Энергетическая безопасность</t>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Г.1.1 руководителей и специалистов организаций, эксплуатирующих электроустановки</t>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Г.2.1 руководителей и специалистов организаций, эксплуатирующих тепловые электрические станции</t>
-  </si>
-  <si>
-    <t>Подготовка по области аттестации Г.2.2 руководителей и специалистов организаций, эксплуатирующих электрические сети</t>
-  </si>
-  <si>
-    <t>Программа повышения квалификации электротехнического персонала</t>
-  </si>
-  <si>
-    <t>Повышение квалификации для руководителей и специалистов теплоснабжающих организаций и потребителей, эксплуатирующих тепломеханическое  оборудование и тепловые сети</t>
-  </si>
-  <si>
-    <t>Повышение квалификации руководителей и специалистов организаций, эксплуатирующих тепловые энергоустановки</t>
-  </si>
-  <si>
-    <t>Повышение квалификации  персонала организаций, осуществляющих эксплуатацию объектов электроэнергетики</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (II группа по электробезопасности до и выше 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (III группа по электробезопасности до 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (III группа по электробезопасности до и выше 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (IV группа по электробезопасности до 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (IV группа по электробезопасности до и выше1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (V группа по электробезопасности до и выше 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (III группа по электробезопасности до и выше 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (III группа по электробезопасности до 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (IV группа по электробезопасности до и выше 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний руководителей и специалистов  электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (IV группа по электробезопасности до 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (V группа по электробезопасности до и выше 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (V группа по электробезопасности до 1000 В)</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников теплоснабжающих и теплосетевых организаций</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей тепловой энергии, эксплуатирующих технологическое оборудование, использующее тепловую энергию</t>
-  </si>
-  <si>
-    <t>Подготовка и проверка знаний работников организаций-потребителей тепловой энергии, эксплуатирующих системы отопления</t>
-  </si>
-  <si>
-    <t>Охрана труда</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения земляных работ</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения ремонтных, монтажных и демонтажных работ зданий и сооружений</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ при размещении, монтаже, техническом обслуживании и ремонте технологического оборудования (включая технологическое оборудование)</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ на высоте</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения пожароопасных работ</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ в ограниченных и замкнутых пространствах (ОЗП)</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения строительных работ, в том числе: - окрасочные работы; - электросварочные и газосварочные работы</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ, связанных с опасностью воздействия сильнодействующих и ядовитых веществ</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения газоопасных работ</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения огневых работ</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ, связанные с эксплуатацией подъемных сооружений</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ, связанные с эксплуатацией тепловых энергоустановок</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ в электроустановках</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы выполнения работ, связанные с эксплуатацией сосудов, работающих под избыточным давлением</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы обращения с животными</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы при выполнении водолазных работ</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ по поиску, идентификации, обезвреживанию и уничтожению взрывоопасных предметов</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ в непосредственной близости от полотна или проезжей части эксплуатируемых автомобильных и железных дорог</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ, на участках с патогенным заражением почвы</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ по валке леса в особо опасных условиях</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ по перемещению тяжеловесных и крупногабаритных грузов при отсутствии машин соответствующей грузоподъемности и разборке покосившихся и опасных (неправильно уложенных) штабелей круглых лесоматериалов</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ с радиоактивными веществами и источниками ионизирующих излучений</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ с ручным инструментом, в том числе с пиротехническим</t>
-  </si>
-  <si>
-    <t>Безопасные методы и приемы работ в театрах</t>
-  </si>
-  <si>
-    <t>Обучение по оказанию первой помощи пострадавшим</t>
-  </si>
-  <si>
-    <t>Обучение по использованию (применению) СИЗ</t>
-  </si>
-  <si>
-    <t>Экологическая безопасность</t>
-  </si>
-  <si>
-    <t>Основы обеспечения экологической безопасности в организации</t>
-  </si>
-  <si>
-    <t>Сбор, транспортирование, обработка, утилизация, обезвреживание, размещение отходов I - IV классов опасности</t>
-  </si>
-  <si>
-    <t>Психология</t>
-  </si>
-  <si>
-    <t>Психологические аспекты охраны труда и безопасности работ на энергетических предприятиях</t>
-  </si>
-  <si>
-    <t>Психологические аспекты управленческого труда для руководителей среднего звена и кадрового резерва (стресс и его последствия, способы преодоления кризисных ситуаций)</t>
-  </si>
-  <si>
-    <t>Психологические аспекты управленческого труда для руководителей среднего звена и кадрового резерва (конфликтология, формирование навыков эффективного общения)</t>
-  </si>
-  <si>
-    <t>Программа повышения квалификации кадрового резерва</t>
-  </si>
-  <si>
-    <t>Тренинг для наставников</t>
-  </si>
-  <si>
-    <t>Формирование навыков эффективного общения</t>
-  </si>
-  <si>
-    <t>Психология и этика деловых отношений</t>
-  </si>
-  <si>
-    <t>Обучение по общим вопросам охраны труда и функционирования СУОТ (А)</t>
-  </si>
-  <si>
-    <t>Программа ПК для лиц, ответственных за обеспечение пожарной безопасности на объектах защиты, в которых могут одновременно находиться 50 и более человек, объектах защиты, отнесенных к категориям повышенной взрывопожароопасности, взрывопожароопасности, пожароопасности</t>
-  </si>
-  <si>
-    <t>Программа ПК электротехнического персонала (обслуживание аккумуляторной батареи)</t>
-  </si>
-  <si>
-    <t>Обучение безопасным методам и приемам выполнения работ при воздействии вредных и (или) опасных производственных факторов, источников опасности, идентифицированных в рамках специальной оценки условий труда и оценки профессиональных рисков (Б)</t>
+    <t>Повышение квалификации персонала организаций, осуществляющих эксплуатацию объектов электроэнергетики</t>
+  </si>
+  <si>
+    <t>Повышение квалификации для руководителей и специалистов теплоснабжающих организаций и потребителей, эксплуатирующих тепломеханическое оборудование и тепловые сети</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний работников организаций-потребителей электрической энергии (IV группа по электробезопасности до и выше 1000 В)</t>
+  </si>
+  <si>
+    <t>Подготовка и проверка знаний руководителей и специалистов электротехнических лабораторий, осуществляющих испытание оборудования в электроустановках потребителей (IV группа по электробезопасности до 1000 В)</t>
+  </si>
+  <si>
+    <t>Обучение безопасным методам и приёмам выполнения работ при воздействии вредных и (или) опасных производственных факторов, источников опасности, идентифицированных в рамках специальной оценки условий труда и оценки профессиональных рисков (Б)</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения земляных работ</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения ремонтных, монтажных и демонтажных работ зданий и сооружений</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ при размещении, монтаже, техническом обслуживании и ремонте технологического оборудования (включая технологическое оборудование)</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ на высоте</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения пожароопасных работ</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ в ограниченных и замкнутых пространствах (ОЗП)</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения строительных работ, в том числе: - окрасочные работы; - электросварочные и газосварочные работы</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ, связанных с опасностью воздействия сильнодействующих и ядовитых веществ</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения газоопасных работ</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения огневых работ</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ, связанные с эксплуатацией тепловых энергоустановок</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ в электроустановках</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ, связанные с эксплуатацией сосудов, работающих под избыточным давлением</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы обращения с животными</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы при выполнении водолазных работ</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ по поиску, идентификации, обезвреживанию и уничтожению взрывоопасных предметов</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ в непосредственной близости от полотна или проезжей части эксплуатируемых автомобильных и железных дорог</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ, на участках с патогенным заражением почвы</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ по валке леса в особо опасных условиях</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ с радиоактивными веществами и источниками ионизирующих излучений</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ с ручным инструментом, в том числе с пиротехническим</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ в театрах</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы выполнения работ, связанные с эксплуатацией подъёмных сооружений</t>
+  </si>
+  <si>
+    <t>Безопасные методы и приёмы работ по перемещению тяжеловесных и крупногабаритных грузов при отсутствии машин соответствующей грузоподъёмности и разборке покосившихся и опасных (неправильно уложенных) штабелей круглых лесоматериалов</t>
   </si>
 </sst>
 </file>
@@ -1672,13 +1564,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5">
         <v>240</v>
       </c>
       <c r="D7" s="5">
-        <v>22600</v>
+        <v>24800</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>7</v>
@@ -1689,7 +1581,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8" s="5">
         <v>240</v>
@@ -1706,7 +1598,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="C9" s="5">
         <v>240</v>
@@ -1723,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5">
         <v>240</v>
@@ -1740,13 +1632,13 @@
         <v>5</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5">
         <v>240</v>
       </c>
       <c r="D11" s="5">
-        <v>32400</v>
+        <v>22600</v>
       </c>
       <c r="E11" s="24" t="s">
         <v>7</v>
@@ -1756,8 +1648,8 @@
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>17</v>
+      <c r="B12" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="C12" s="5">
         <v>240</v>
@@ -1774,7 +1666,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="5">
         <v>240</v>
@@ -1790,14 +1682,14 @@
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>19</v>
+      <c r="B14" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="C14" s="5">
         <v>240</v>
       </c>
       <c r="D14" s="5">
-        <v>24800</v>
+        <v>32400</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>7</v>
@@ -1808,7 +1700,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="5">
         <v>240</v>
@@ -1825,7 +1717,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="5">
         <v>240</v>
@@ -1858,7 +1750,7 @@
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="5">
@@ -1876,13 +1768,13 @@
         <v>5</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="5">
         <v>240</v>
       </c>
       <c r="D19" s="5">
-        <v>24800</v>
+        <v>22600</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>7</v>
@@ -1893,7 +1785,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C20" s="5">
         <v>240</v>
@@ -1909,8 +1801,8 @@
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>26</v>
+      <c r="B21" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="C21" s="5">
         <v>240</v>
@@ -1927,9 +1819,9 @@
         <v>5</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="5">
+        <v>34</v>
+      </c>
+      <c r="C22" s="6">
         <v>240</v>
       </c>
       <c r="D22" s="5">
@@ -1943,10 +1835,10 @@
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="B23" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5">
         <v>240</v>
       </c>
       <c r="D23" s="5">
@@ -1961,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C24" s="5">
         <v>240</v>
@@ -1978,13 +1870,13 @@
         <v>5</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D25" s="5">
-        <v>8500</v>
+        <v>22600</v>
       </c>
       <c r="E25" s="24" t="s">
         <v>7</v>
@@ -1995,13 +1887,13 @@
         <v>5</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C26" s="5">
         <v>240</v>
       </c>
       <c r="D26" s="5">
-        <v>23000</v>
+        <v>22600</v>
       </c>
       <c r="E26" s="24" t="s">
         <v>7</v>
@@ -2011,14 +1903,14 @@
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="17" t="s">
-        <v>31</v>
+      <c r="B27" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="C27" s="5">
         <v>240</v>
       </c>
       <c r="D27" s="5">
-        <v>23000</v>
+        <v>24800</v>
       </c>
       <c r="E27" s="24" t="s">
         <v>7</v>
@@ -2029,13 +1921,13 @@
         <v>5</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C28" s="5">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="D28" s="5">
-        <v>23000</v>
+        <v>8500</v>
       </c>
       <c r="E28" s="24" t="s">
         <v>7</v>
@@ -2046,7 +1938,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="C29" s="5">
         <v>240</v>
@@ -2063,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C30" s="5">
         <v>240</v>
@@ -2080,7 +1972,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="C31" s="5">
         <v>240</v>
@@ -2097,13 +1989,13 @@
         <v>5</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="C32" s="5">
         <v>240</v>
       </c>
       <c r="D32" s="5">
-        <v>28000</v>
+        <v>23000</v>
       </c>
       <c r="E32" s="24" t="s">
         <v>7</v>
@@ -2114,7 +2006,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C33" s="5">
         <v>240</v>
@@ -2131,7 +2023,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="C34" s="5">
         <v>240</v>
@@ -2148,13 +2040,13 @@
         <v>5</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C35" s="5">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="D35" s="5">
-        <v>33000</v>
+        <v>28000</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>7</v>
@@ -2165,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="C36" s="5">
         <v>240</v>
@@ -2182,13 +2074,13 @@
         <v>5</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="C37" s="5">
         <v>240</v>
       </c>
       <c r="D37" s="5">
-        <v>22600</v>
+        <v>23000</v>
       </c>
       <c r="E37" s="24" t="s">
         <v>7</v>
@@ -2199,13 +2091,13 @@
         <v>5</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="C38" s="5">
         <v>240</v>
       </c>
       <c r="D38" s="5">
-        <v>22600</v>
+        <v>23000</v>
       </c>
       <c r="E38" s="24" t="s">
         <v>7</v>
@@ -2216,13 +2108,13 @@
         <v>5</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="C39" s="5">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="D39" s="5">
-        <v>22600</v>
+        <v>33000</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>7</v>
@@ -2233,7 +2125,7 @@
         <v>5</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C40" s="5">
         <v>240</v>
@@ -2250,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C41" s="5">
         <v>240</v>
@@ -2264,10 +2156,10 @@
     </row>
     <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="C42" s="8">
         <v>40</v>
@@ -2282,10 +2174,10 @@
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C43" s="5">
         <v>40</v>
@@ -2300,10 +2192,10 @@
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="C44" s="5">
         <v>40</v>
@@ -2318,64 +2210,64 @@
     </row>
     <row r="45" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="5">
-        <v>72</v>
-      </c>
-      <c r="D45" s="10">
-        <v>58000</v>
+        <v>57</v>
+      </c>
+      <c r="C45" s="6">
+        <v>40</v>
+      </c>
+      <c r="D45" s="11">
+        <v>3850</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="F45" s="5"/>
     </row>
-    <row r="46" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B46" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="5">
-        <v>24</v>
-      </c>
-      <c r="D46" s="11">
-        <v>10500</v>
+      <c r="C46" s="6">
+        <v>72</v>
+      </c>
+      <c r="D46" s="10">
+        <v>23000</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="F46" s="5"/>
     </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="C47" s="6">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D47" s="10">
-        <v>7500</v>
+        <v>23000</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="F47" s="5"/>
     </row>
-    <row r="48" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="C48" s="5">
         <v>24</v>
@@ -2384,112 +2276,112 @@
         <v>7500</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="F48" s="5"/>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="C49" s="6">
         <v>24</v>
       </c>
       <c r="D49" s="10">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="F49" s="5"/>
     </row>
     <row r="50" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="5">
+        <v>55</v>
+      </c>
+      <c r="C50" s="6">
         <v>24</v>
       </c>
       <c r="D50" s="10">
         <v>7500</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="F50" s="5"/>
     </row>
     <row r="51" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" s="6">
+        <v>24</v>
+      </c>
+      <c r="D51" s="10">
+        <v>7500</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="5">
-        <v>40</v>
-      </c>
-      <c r="D51" s="10">
-        <v>7200</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="F51" s="6"/>
-    </row>
-    <row r="52" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C52" s="5">
-        <v>40</v>
+      <c r="C52" s="6">
+        <v>72</v>
       </c>
       <c r="D52" s="10">
-        <v>7200</v>
+        <v>23000</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="F52" s="6"/>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53" s="5">
-        <v>72</v>
-      </c>
-      <c r="D53" s="10">
-        <v>10500</v>
+        <v>51</v>
+      </c>
+      <c r="C53" s="6">
+        <v>24</v>
+      </c>
+      <c r="D53" s="11">
+        <v>7500</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="F53" s="5"/>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="C54" s="5">
         <v>72</v>
       </c>
       <c r="D54" s="10">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="E54" s="23" t="s">
         <v>7</v>
@@ -2498,16 +2390,16 @@
     </row>
     <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C55" s="5">
         <v>72</v>
       </c>
       <c r="D55" s="10">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="E55" s="23" t="s">
         <v>7</v>
@@ -2516,106 +2408,106 @@
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C56" s="5">
+        <v>45</v>
+      </c>
+      <c r="C56" s="6">
         <v>72</v>
       </c>
       <c r="D56" s="10">
-        <v>10500</v>
+        <v>23000</v>
       </c>
       <c r="E56" s="23" t="s">
         <v>7</v>
       </c>
       <c r="F56" s="5"/>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="5">
+        <v>54</v>
+      </c>
+      <c r="C57" s="6">
+        <v>24</v>
+      </c>
+      <c r="D57" s="10">
+        <v>6825</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="6">
+        <v>24</v>
+      </c>
+      <c r="D58" s="10">
+        <v>6825</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" s="5"/>
+    </row>
+    <row r="59" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" s="6">
+        <v>24</v>
+      </c>
+      <c r="D59" s="10">
+        <v>6825</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" s="5"/>
+    </row>
+    <row r="60" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="6">
+        <v>24</v>
+      </c>
+      <c r="D60" s="10">
+        <v>2750</v>
+      </c>
+      <c r="E60" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="F60" s="5"/>
+    </row>
+    <row r="61" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C61" s="6">
         <v>72</v>
       </c>
-      <c r="D57" s="10">
-        <v>10500</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" s="5"/>
-    </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="5">
-        <v>72</v>
-      </c>
-      <c r="D58" s="10">
-        <v>10500</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="5"/>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59" s="5">
-        <v>72</v>
-      </c>
-      <c r="D59" s="10">
-        <v>10500</v>
-      </c>
-      <c r="E59" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="5"/>
-    </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" s="5">
-        <v>72</v>
-      </c>
-      <c r="D60" s="10">
-        <v>10500</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="5"/>
-    </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="5">
-        <v>80</v>
-      </c>
       <c r="D61" s="10">
-        <v>11500</v>
+        <v>23000</v>
       </c>
       <c r="E61" s="23" t="s">
         <v>7</v>
@@ -2624,34 +2516,34 @@
     </row>
     <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" s="5">
+        <v>49</v>
+      </c>
+      <c r="C62" s="6">
         <v>72</v>
       </c>
       <c r="D62" s="10">
-        <v>10500</v>
+        <v>23000</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="F62" s="5"/>
     </row>
     <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="C63" s="5">
         <v>72</v>
       </c>
       <c r="D63" s="10">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="E63" s="23" t="s">
         <v>7</v>
@@ -2660,16 +2552,16 @@
     </row>
     <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="C64" s="5">
         <v>72</v>
       </c>
       <c r="D64" s="10">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="E64" s="23" t="s">
         <v>7</v>
@@ -2678,10 +2570,10 @@
     </row>
     <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="C65" s="5">
         <v>72</v>
@@ -2696,34 +2588,34 @@
     </row>
     <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="6">
+        <v>149</v>
+      </c>
+      <c r="C66" s="5">
         <v>72</v>
       </c>
       <c r="D66" s="10">
-        <v>23000</v>
+        <v>10500</v>
       </c>
       <c r="E66" s="23" t="s">
         <v>7</v>
       </c>
       <c r="F66" s="5"/>
     </row>
-    <row r="67" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="6">
+        <v>150</v>
+      </c>
+      <c r="C67" s="5">
         <v>72</v>
       </c>
       <c r="D67" s="10">
-        <v>23000</v>
+        <v>10500</v>
       </c>
       <c r="E67" s="23" t="s">
         <v>7</v>
@@ -2732,34 +2624,34 @@
     </row>
     <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C68" s="6">
+        <v>151</v>
+      </c>
+      <c r="C68" s="5">
         <v>72</v>
       </c>
       <c r="D68" s="10">
-        <v>23000</v>
+        <v>10500</v>
       </c>
       <c r="E68" s="23" t="s">
         <v>7</v>
       </c>
       <c r="F68" s="5"/>
     </row>
-    <row r="69" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B69" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C69" s="5">
         <v>72</v>
       </c>
-      <c r="C69" s="6">
-        <v>72</v>
-      </c>
       <c r="D69" s="10">
-        <v>23000</v>
+        <v>10500</v>
       </c>
       <c r="E69" s="23" t="s">
         <v>7</v>
@@ -2768,118 +2660,118 @@
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="6">
+        <v>162</v>
+      </c>
+      <c r="C70" s="5">
         <v>72</v>
       </c>
       <c r="D70" s="10">
-        <v>23000</v>
+        <v>10500</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="F70" s="6"/>
     </row>
     <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C71" s="6">
+        <v>163</v>
+      </c>
+      <c r="C71" s="5">
+        <v>80</v>
+      </c>
+      <c r="D71" s="10">
+        <v>11500</v>
+      </c>
+      <c r="E71" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="5"/>
+    </row>
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" s="5">
         <v>72</v>
       </c>
-      <c r="D71" s="10">
-        <v>23000</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" s="5"/>
-    </row>
-    <row r="72" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B72" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" s="6">
-        <v>24</v>
-      </c>
-      <c r="D72" s="11">
-        <v>7500</v>
+      <c r="D72" s="10">
+        <v>10500</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C73" s="6">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="C73" s="5">
+        <v>72</v>
       </c>
       <c r="D73" s="10">
-        <v>6825</v>
+        <v>10500</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="F73" s="6"/>
     </row>
     <row r="74" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B74" s="18" t="s">
-        <v>77</v>
+        <v>35</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="C74" s="6">
-        <v>24</v>
-      </c>
-      <c r="D74" s="10">
-        <v>6825</v>
+        <v>16</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="1:6" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="C75" s="6">
         <v>24</v>
       </c>
       <c r="D75" s="10">
-        <v>6825</v>
+        <v>7500</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C76" s="6">
         <v>24</v>
@@ -2888,124 +2780,124 @@
         <v>7500</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="F76" s="5"/>
     </row>
     <row r="77" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C77" s="6">
+        <v>38</v>
+      </c>
+      <c r="C77" s="5">
         <v>24</v>
       </c>
       <c r="D77" s="10">
         <v>7500</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="F77" s="5"/>
     </row>
     <row r="78" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C78" s="6">
+        <v>164</v>
+      </c>
+      <c r="C78" s="5">
         <v>24</v>
       </c>
       <c r="D78" s="10">
-        <v>6825</v>
+        <v>7500</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C79" s="5">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D79" s="10">
-        <v>7500</v>
+        <v>7200</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C80" s="6">
-        <v>24</v>
+        <v>41</v>
+      </c>
+      <c r="C80" s="5">
+        <v>40</v>
       </c>
       <c r="D80" s="10">
-        <v>2750</v>
+        <v>7200</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C81" s="6">
-        <v>40</v>
-      </c>
-      <c r="D81" s="11">
-        <v>3850</v>
+        <v>36</v>
+      </c>
+      <c r="C81" s="5">
+        <v>72</v>
+      </c>
+      <c r="D81" s="10">
+        <v>58000</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="F81" s="6"/>
     </row>
     <row r="82" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" s="6">
-        <v>16</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>87</v>
+        <v>35</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="5">
+        <v>24</v>
+      </c>
+      <c r="D82" s="11">
+        <v>10500</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="C83" s="6">
         <v>24</v>
@@ -3020,10 +2912,10 @@
     </row>
     <row r="84" spans="1:6" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="C84" s="8">
         <v>24</v>
@@ -3035,12 +2927,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="C85" s="6">
         <v>24</v>
@@ -3052,12 +2944,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C86" s="6">
         <v>24</v>
@@ -3071,10 +2963,10 @@
     </row>
     <row r="87" spans="1:6" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C87" s="6">
         <v>256</v>
@@ -3088,10 +2980,10 @@
     </row>
     <row r="88" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C88" s="4">
         <v>20</v>
@@ -3100,15 +2992,15 @@
         <v>2200</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C89" s="4">
         <v>20</v>
@@ -3117,15 +3009,15 @@
         <v>4400</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="C90" s="4">
         <v>20</v>
@@ -3134,15 +3026,15 @@
         <v>4400</v>
       </c>
       <c r="E90" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C91" s="4">
         <v>20</v>
@@ -3151,15 +3043,15 @@
         <v>4400</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="C92" s="4">
         <v>20</v>
@@ -3168,15 +3060,15 @@
         <v>4400</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="C93" s="4">
         <v>20</v>
@@ -3185,15 +3077,15 @@
         <v>4400</v>
       </c>
       <c r="E93" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="C94" s="4">
         <v>20</v>
@@ -3202,15 +3094,15 @@
         <v>4400</v>
       </c>
       <c r="E94" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C95" s="4">
         <v>20</v>
@@ -3219,15 +3111,15 @@
         <v>4400</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C96" s="4">
         <v>20</v>
@@ -3236,15 +3128,15 @@
         <v>4400</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C97" s="4">
         <v>20</v>
@@ -3253,15 +3145,15 @@
         <v>4400</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C98" s="4">
         <v>20</v>
@@ -3270,15 +3162,15 @@
         <v>4400</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="C99" s="4">
         <v>20</v>
@@ -3287,15 +3179,15 @@
         <v>4400</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C100" s="4">
         <v>20</v>
@@ -3304,15 +3196,15 @@
         <v>4400</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C101" s="4">
         <v>20</v>
@@ -3321,15 +3213,15 @@
         <v>4400</v>
       </c>
       <c r="E101" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="76.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="C102" s="4">
         <v>20</v>
@@ -3338,15 +3230,15 @@
         <v>4400</v>
       </c>
       <c r="E102" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="C103" s="4">
         <v>20</v>
@@ -3355,15 +3247,15 @@
         <v>4400</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="C104" s="4">
         <v>20</v>
@@ -3372,15 +3264,15 @@
         <v>4400</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="C105" s="4">
         <v>20</v>
@@ -3389,15 +3281,15 @@
         <v>4400</v>
       </c>
       <c r="E105" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="C106" s="4">
         <v>20</v>
@@ -3406,15 +3298,15 @@
         <v>4400</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="C107" s="4">
         <v>20</v>
@@ -3423,15 +3315,15 @@
         <v>4400</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="C108" s="4">
         <v>20</v>
@@ -3440,15 +3332,15 @@
         <v>4400</v>
       </c>
       <c r="E108" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C109" s="4">
         <v>20</v>
@@ -3457,32 +3349,32 @@
         <v>4400</v>
       </c>
       <c r="E109" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C110" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D110" s="2">
         <v>4400</v>
       </c>
       <c r="E110" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C111" s="4">
         <v>20</v>
@@ -3491,15 +3383,15 @@
         <v>4400</v>
       </c>
       <c r="E111" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B112" s="20" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="C112" s="4">
         <v>20</v>
@@ -3508,15 +3400,15 @@
         <v>4400</v>
       </c>
       <c r="E112" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="C113" s="4">
         <v>20</v>
@@ -3525,15 +3417,15 @@
         <v>4400</v>
       </c>
       <c r="E113" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C114" s="4">
         <v>20</v>
@@ -3542,15 +3434,15 @@
         <v>4400</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="C115" s="4">
         <v>20</v>
@@ -3559,15 +3451,15 @@
         <v>4400</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C116" s="4">
         <v>20</v>
@@ -3576,15 +3468,15 @@
         <v>4400</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B117" s="20" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C117" s="4">
         <v>20</v>
@@ -3593,15 +3485,15 @@
         <v>4400</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B118" s="20" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C118" s="4">
         <v>20</v>
@@ -3610,15 +3502,15 @@
         <v>4400</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B119" s="20" t="s">
         <v>96</v>
-      </c>
-      <c r="B119" s="20" t="s">
-        <v>128</v>
       </c>
       <c r="C119" s="4">
         <v>20</v>
@@ -3627,15 +3519,15 @@
         <v>4400</v>
       </c>
       <c r="E119" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B120" s="20" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="C120" s="4">
         <v>20</v>
@@ -3644,15 +3536,15 @@
         <v>4400</v>
       </c>
       <c r="E120" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C121" s="4">
         <v>20</v>
@@ -3661,15 +3553,15 @@
         <v>4400</v>
       </c>
       <c r="E121" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B122" s="20" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C122" s="4">
         <v>20</v>
@@ -3678,15 +3570,15 @@
         <v>4400</v>
       </c>
       <c r="E122" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C123" s="4">
         <v>20</v>
@@ -3695,15 +3587,15 @@
         <v>4400</v>
       </c>
       <c r="E123" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B124" s="20" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C124" s="4">
         <v>20</v>
@@ -3712,15 +3604,15 @@
         <v>4400</v>
       </c>
       <c r="E124" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C125" s="4">
         <v>20</v>
@@ -3729,15 +3621,15 @@
         <v>4400</v>
       </c>
       <c r="E125" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B126" s="20" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="C126" s="4">
         <v>20</v>
@@ -3746,15 +3638,15 @@
         <v>4400</v>
       </c>
       <c r="E126" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B127" s="20" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="C127" s="4">
         <v>20</v>
@@ -3763,15 +3655,15 @@
         <v>4400</v>
       </c>
       <c r="E127" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="C128" s="4">
         <v>20</v>
@@ -3780,15 +3672,15 @@
         <v>4400</v>
       </c>
       <c r="E128" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="C129" s="4">
         <v>20</v>
@@ -3797,15 +3689,15 @@
         <v>4400</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B130" s="21" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="C130" s="4">
         <v>20</v>
@@ -3814,15 +3706,15 @@
         <v>4400</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B131" s="21" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="C131" s="4">
         <v>20</v>
@@ -3831,15 +3723,15 @@
         <v>4400</v>
       </c>
       <c r="E131" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="C132" s="4">
         <v>20</v>
@@ -3848,15 +3740,15 @@
         <v>4400</v>
       </c>
       <c r="E132" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="C133" s="4">
         <v>20</v>
@@ -3865,15 +3757,15 @@
         <v>4400</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="C134" s="4">
         <v>20</v>
@@ -3882,15 +3774,15 @@
         <v>4400</v>
       </c>
       <c r="E134" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="C135" s="4">
         <v>20</v>
@@ -3899,15 +3791,15 @@
         <v>4400</v>
       </c>
       <c r="E135" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="B136" s="25" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="C136" s="4">
         <v>20</v>
@@ -3916,15 +3808,15 @@
         <v>4400</v>
       </c>
       <c r="E136" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="C137" s="4">
         <v>40</v>
@@ -3933,15 +3825,15 @@
         <v>7900</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="C138" s="4">
         <v>40</v>
@@ -3950,15 +3842,15 @@
         <v>7900</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="C139" s="4">
         <v>40</v>
@@ -3967,15 +3859,15 @@
         <v>7900</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="C140" s="8">
         <v>72</v>
@@ -3984,49 +3876,49 @@
         <v>7900</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C141" s="6">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D141" s="10">
         <v>7900</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B142" s="18" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C142" s="6">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D142" s="10">
         <v>7900</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="C143" s="6">
         <v>40</v>
@@ -4035,49 +3927,49 @@
         <v>7900</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="C144" s="8">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D144" s="9">
         <v>7900</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="C145" s="6">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D145" s="10">
         <v>7900</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B146" s="18" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="C146" s="6">
         <v>72</v>
@@ -4091,10 +3983,10 @@
     </row>
     <row r="147" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="C147" s="6">
         <v>72</v>
@@ -4108,10 +4000,10 @@
     </row>
     <row r="148" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B148" s="18" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="C148" s="6">
         <v>72</v>
@@ -4125,10 +4017,10 @@
     </row>
     <row r="149" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="C149" s="6">
         <v>72</v>
@@ -4140,63 +4032,63 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B150" s="16" t="s">
-        <v>160</v>
+        <v>103</v>
+      </c>
+      <c r="B150" s="15" t="s">
+        <v>184</v>
       </c>
       <c r="C150" s="8">
         <v>72</v>
       </c>
       <c r="D150" s="9">
-        <v>8180</v>
+        <v>7900</v>
       </c>
       <c r="E150" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B151" s="17" t="s">
-        <v>161</v>
+        <v>103</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>113</v>
       </c>
       <c r="C151" s="6">
         <v>72</v>
       </c>
       <c r="D151" s="10">
-        <v>8180</v>
+        <v>7900</v>
       </c>
       <c r="E151" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B152" s="17" t="s">
-        <v>162</v>
+        <v>103</v>
+      </c>
+      <c r="B152" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="C152" s="6">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D152" s="10">
-        <v>8180</v>
+        <v>7900</v>
       </c>
       <c r="E152" s="23" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="C153" s="6">
         <v>72</v>
@@ -4210,10 +4102,10 @@
     </row>
     <row r="154" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="C154" s="6">
         <v>72</v>
@@ -4227,10 +4119,10 @@
     </row>
     <row r="155" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C155" s="6">
         <v>72</v>
@@ -4242,63 +4134,63 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B156" s="15" t="s">
-        <v>166</v>
+        <v>103</v>
+      </c>
+      <c r="B156" s="16" t="s">
+        <v>116</v>
       </c>
       <c r="C156" s="8">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D156" s="9">
-        <v>7900</v>
+        <v>8180</v>
       </c>
       <c r="E156" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B157" s="18" t="s">
-        <v>167</v>
+        <v>103</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>118</v>
       </c>
       <c r="C157" s="6">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D157" s="10">
-        <v>7900</v>
+        <v>8180</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B158" s="18" t="s">
-        <v>168</v>
+        <v>103</v>
+      </c>
+      <c r="B158" s="17" t="s">
+        <v>117</v>
       </c>
       <c r="C158" s="6">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D158" s="10">
-        <v>7900</v>
+        <v>8180</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>207</v>
+        <v>136</v>
       </c>
       <c r="C159" s="8">
         <v>16</v>
@@ -4312,10 +4204,10 @@
     </row>
     <row r="160" spans="1:5" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B160" s="18" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="C160" s="5">
         <v>16</v>
@@ -4329,10 +4221,10 @@
     </row>
     <row r="161" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C161" s="5">
         <v>16</v>
@@ -4346,10 +4238,10 @@
     </row>
     <row r="162" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C162" s="5">
         <v>16</v>
@@ -4363,10 +4255,10 @@
     </row>
     <row r="163" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C163" s="5">
         <v>16</v>
@@ -4380,10 +4272,10 @@
     </row>
     <row r="164" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C164" s="5">
         <v>16</v>
@@ -4397,10 +4289,10 @@
     </row>
     <row r="165" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C165" s="5">
         <v>16</v>
@@ -4414,10 +4306,10 @@
     </row>
     <row r="166" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B166" s="20" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C166" s="5">
         <v>16</v>
@@ -4431,10 +4323,10 @@
     </row>
     <row r="167" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C167" s="5">
         <v>16</v>
@@ -4448,10 +4340,10 @@
     </row>
     <row r="168" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B168" s="20" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="C168" s="5">
         <v>16</v>
@@ -4465,10 +4357,10 @@
     </row>
     <row r="169" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C169" s="5">
         <v>16</v>
@@ -4482,10 +4374,10 @@
     </row>
     <row r="170" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C170" s="5">
         <v>16</v>
@@ -4499,10 +4391,10 @@
     </row>
     <row r="171" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B171" s="20" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C171" s="5">
         <v>16</v>
@@ -4516,10 +4408,10 @@
     </row>
     <row r="172" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C172" s="5">
         <v>16</v>
@@ -4533,10 +4425,10 @@
     </row>
     <row r="173" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C173" s="5">
         <v>16</v>
@@ -4550,10 +4442,10 @@
     </row>
     <row r="174" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C174" s="5">
         <v>16</v>
@@ -4567,10 +4459,10 @@
     </row>
     <row r="175" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C175" s="5">
         <v>16</v>
@@ -4584,10 +4476,10 @@
     </row>
     <row r="176" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="C176" s="5">
         <v>16</v>
@@ -4601,10 +4493,10 @@
     </row>
     <row r="177" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B177" s="20" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="C177" s="5">
         <v>16</v>
@@ -4618,10 +4510,10 @@
     </row>
     <row r="178" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B178" s="20" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C178" s="5">
         <v>16</v>
@@ -4635,10 +4527,10 @@
     </row>
     <row r="179" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B179" s="20" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C179" s="5">
         <v>16</v>
@@ -4652,10 +4544,10 @@
     </row>
     <row r="180" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C180" s="5">
         <v>16</v>
@@ -4669,10 +4561,10 @@
     </row>
     <row r="181" spans="1:5" ht="38.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B181" s="20" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C181" s="5">
         <v>16</v>
@@ -4686,10 +4578,10 @@
     </row>
     <row r="182" spans="1:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B182" s="20" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C182" s="5">
         <v>16</v>
@@ -4703,10 +4595,10 @@
     </row>
     <row r="183" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B183" s="20" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C183" s="5">
         <v>16</v>
@@ -4720,10 +4612,10 @@
     </row>
     <row r="184" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B184" s="20" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C184" s="5">
         <v>16</v>
@@ -4737,10 +4629,10 @@
     </row>
     <row r="185" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="C185" s="8">
         <v>16</v>
@@ -4749,15 +4641,15 @@
         <v>2100</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="B186" s="18" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="C186" s="6">
         <v>16</v>
@@ -4766,15 +4658,15 @@
         <v>2100</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="14" t="s">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="C187" s="8">
         <v>72</v>
@@ -4783,15 +4675,15 @@
         <v>7500</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="14" t="s">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="C188" s="6">
         <v>72</v>
@@ -4800,15 +4692,15 @@
         <v>7500</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="14" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="B189" s="16" t="s">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="C189" s="4">
         <v>16</v>
@@ -4817,15 +4709,15 @@
         <v>21000</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="B190" s="18" t="s">
-        <v>201</v>
+        <v>128</v>
+      </c>
+      <c r="B190" s="17" t="s">
+        <v>132</v>
       </c>
       <c r="C190" s="5">
         <v>16</v>
@@ -4834,15 +4726,15 @@
         <v>21000</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="14" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="C191" s="5">
         <v>16</v>
@@ -4851,15 +4743,15 @@
         <v>21000</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="B192" s="17" t="s">
-        <v>203</v>
+        <v>128</v>
+      </c>
+      <c r="B192" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="C192" s="5">
         <v>16</v>
@@ -4868,15 +4760,15 @@
         <v>21000</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="14" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="C193" s="5">
         <v>16</v>
@@ -4885,15 +4777,15 @@
         <v>21000</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="14" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="B194" s="18" t="s">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="C194" s="5">
         <v>16</v>
@@ -4902,15 +4794,15 @@
         <v>21000</v>
       </c>
       <c r="E194" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="14" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="C195" s="5">
         <v>16</v>
@@ -4919,10 +4811,13 @@
         <v>21000</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B190:E195">
+    <sortCondition ref="B189:B195"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
